--- a/Code/Jupiter/Connect4/Selected EVAL_PPO_results.xlsx
+++ b/Code/Jupiter/Connect4/Selected EVAL_PPO_results.xlsx
@@ -10,6 +10,9 @@
   <sheets>
     <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId3"/>
   </sheets>
+  <definedNames>
+    <definedName function="false" hidden="true" localSheetId="0" name="_xlnm._FilterDatabase" vbProcedure="false">Sheet1!$A$1:$Q$5</definedName>
+  </definedNames>
   <calcPr iterateCount="100" refMode="A1" iterate="false" iterateDelta="0.0001"/>
   <extLst>
     <ext xmlns:loext="http://schemas.libreoffice.org/" uri="{7626C862-2A13-11E5-B345-FEFF819CDC9F}">
@@ -73,16 +76,16 @@
     <t xml:space="preserve">GLOBAL_SCORE</t>
   </si>
   <si>
-    <t xml:space="preserve">PPO_8</t>
-  </si>
-  <si>
-    <t xml:space="preserve">PPO_10</t>
-  </si>
-  <si>
-    <t xml:space="preserve">PPO_11</t>
-  </si>
-  <si>
-    <t xml:space="preserve">PPO_12</t>
+    <t xml:space="preserve">PPO_14</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PPO_404</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PPO_405</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PPO_406</t>
   </si>
 </sst>
 </file>
@@ -176,21 +179,13 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="2">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
   </cellXfs>
@@ -202,7 +197,28 @@
     <cellStyle name="Currency [0]" xfId="18" builtinId="7"/>
     <cellStyle name="Percent" xfId="19" builtinId="5"/>
   </cellStyles>
+  <dxfs count="2">
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FF000000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FF000000"/>
+          <bgColor rgb="FF000000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+  </dxfs>
 </styleSheet>
+</file>
+
+<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -386,287 +402,323 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:Q1048576"/>
-  <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="15" customHeight="true" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="8.453125" defaultRowHeight="15" customHeight="true" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="17.49"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="8.93"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="9.48"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="1" width="8.39"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="1" width="8.75"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="1" width="7.02"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="14" min="7" style="1" width="12.21"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="15" min="15" style="1" width="13.21"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="16" min="16" style="1" width="15.19"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="17" min="17" style="1" width="17.94"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="19.31"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="10.3"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="11.3"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="10.2"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="0" width="10.57"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="0" width="8.84"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="14" min="7" style="0" width="14.03"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="16" min="15" style="0" width="15.03"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="17" min="17" style="0" width="17.94"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="2" t="s">
+      <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="2" t="s">
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="2" t="s">
+      <c r="D1" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="2" t="s">
+      <c r="E1" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="2" t="s">
+      <c r="F1" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="2" t="s">
+      <c r="G1" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="2" t="s">
+      <c r="H1" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="2" t="s">
+      <c r="I1" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="J1" s="2" t="s">
+      <c r="J1" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="K1" s="2" t="s">
+      <c r="K1" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="L1" s="2" t="s">
+      <c r="L1" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="M1" s="2" t="s">
+      <c r="M1" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="N1" s="2" t="s">
+      <c r="N1" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="O1" s="2" t="s">
+      <c r="O1" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="P1" s="2" t="s">
+      <c r="P1" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="Q1" s="2" t="s">
+      <c r="Q1" s="1" t="s">
         <v>16</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="1" t="s">
+      <c r="A2" s="0" t="s">
         <v>17</v>
       </c>
-      <c r="B2" s="1" t="n">
-        <v>0.021095</v>
-      </c>
-      <c r="C2" s="1" t="n">
+      <c r="B2" s="0" t="n">
+        <v>0.020415</v>
+      </c>
+      <c r="C2" s="0" t="n">
         <v>0</v>
       </c>
-      <c r="D2" s="1" t="n">
-        <v>0.985</v>
-      </c>
-      <c r="E2" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="F2" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="G2" s="1" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="H2" s="1" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="I2" s="1" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="J2" s="1" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="K2" s="1" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="L2" s="1" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="M2" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="N2" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="O2" s="1" t="n">
+      <c r="D2" s="0" t="n">
+        <v>0.975</v>
+      </c>
+      <c r="E2" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="F2" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="G2" s="0" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="H2" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="I2" s="0" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="J2" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="K2" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="L2" s="0" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="M2" s="0" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="N2" s="0" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="O2" s="0" t="n">
         <v>0</v>
       </c>
-      <c r="P2" s="1" t="n">
+      <c r="P2" s="0" t="n">
         <v>0</v>
       </c>
-      <c r="Q2" s="1" t="n">
-        <v>0.257818996948599</v>
+      <c r="Q2" s="0" t="n">
+        <v>0.20117693157976</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="1" t="s">
+      <c r="A3" s="0" t="s">
         <v>18</v>
       </c>
-      <c r="B3" s="1" t="n">
-        <v>0.021544</v>
-      </c>
-      <c r="C3" s="1" t="n">
+      <c r="B3" s="0" t="n">
+        <v>0.022379</v>
+      </c>
+      <c r="C3" s="0" t="n">
         <v>0</v>
       </c>
-      <c r="D3" s="1" t="n">
-        <v>0.99</v>
-      </c>
-      <c r="E3" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="F3" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="G3" s="1" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="H3" s="1" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="I3" s="1" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="J3" s="1" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="K3" s="1" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="L3" s="1" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="M3" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="N3" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="O3" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="P3" s="1" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="Q3" s="1" t="n">
-        <v>0.482158176149272</v>
+      <c r="D3" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="E3" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="F3" s="0" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="G3" s="0" t="n">
+        <v>0.22</v>
+      </c>
+      <c r="H3" s="0" t="n">
+        <v>0.32</v>
+      </c>
+      <c r="I3" s="0" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="J3" s="0" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="K3" s="0" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="L3" s="0" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="M3" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="N3" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="O3" s="0" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="P3" s="0" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="Q3" s="0" t="n">
+        <v>0.589623210982221</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="1" t="s">
+      <c r="A4" s="0" t="s">
         <v>19</v>
       </c>
-      <c r="B4" s="1" t="n">
-        <v>0.020717</v>
-      </c>
-      <c r="C4" s="1" t="n">
+      <c r="B4" s="0" t="n">
+        <v>0.019964</v>
+      </c>
+      <c r="C4" s="0" t="n">
         <v>0</v>
       </c>
-      <c r="D4" s="1" t="n">
-        <v>0.98</v>
-      </c>
-      <c r="E4" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="F4" s="1" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="G4" s="1" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="H4" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="I4" s="1" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="J4" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="K4" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="L4" s="1" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="M4" s="1" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="N4" s="1" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="O4" s="1" t="n">
+      <c r="D4" s="0" t="n">
+        <v>0.995</v>
+      </c>
+      <c r="E4" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="F4" s="0" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="G4" s="0" t="n">
+        <v>0.77</v>
+      </c>
+      <c r="H4" s="0" t="n">
+        <v>0.23</v>
+      </c>
+      <c r="I4" s="0" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="J4" s="0" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="K4" s="0" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="L4" s="0" t="n">
         <v>0</v>
       </c>
-      <c r="P4" s="1" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="Q4" s="1" t="n">
-        <v>0.42269002103306</v>
+      <c r="M4" s="0" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="N4" s="0" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="O4" s="0" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="P4" s="0" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="Q4" s="0" t="n">
+        <v>0.483490164565591</v>
       </c>
     </row>
-    <row r="5" s="3" customFormat="true" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A5" s="3" t="s">
+    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A5" s="0" t="s">
         <v>20</v>
       </c>
-      <c r="B5" s="3" t="n">
-        <v>0.019387</v>
-      </c>
-      <c r="C5" s="3" t="n">
+      <c r="B5" s="0" t="n">
+        <v>0.019692</v>
+      </c>
+      <c r="C5" s="0" t="n">
         <v>0</v>
       </c>
-      <c r="D5" s="3" t="n">
-        <v>0.98</v>
-      </c>
-      <c r="E5" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="F5" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="G5" s="3" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="H5" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="I5" s="3" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="J5" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="K5" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="L5" s="3" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="M5" s="3" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="N5" s="3" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="O5" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="P5" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q5" s="3" t="n">
-        <v>0.201205192477234</v>
+      <c r="D5" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="E5" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="F5" s="0" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="G5" s="0" t="n">
+        <v>0.74</v>
+      </c>
+      <c r="H5" s="0" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="I5" s="0" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="J5" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="K5" s="0" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="L5" s="0" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="M5" s="0" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="N5" s="0" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="O5" s="0" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="P5" s="0" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="Q5" s="0" t="n">
+        <v>0.518408018178489</v>
       </c>
     </row>
-    <row r="1048576" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="1048540" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1048541" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1048542" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1048543" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1048544" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1048545" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1048546" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1048547" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1048548" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1048549" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1048550" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1048551" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1048552" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1048553" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1048554" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1048555" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1048556" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1048557" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1048558" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1048559" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1048560" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1048561" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1048562" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1048563" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1048564" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1048565" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1048566" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1048567" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1048568" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1048569" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1048570" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1048571" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1048572" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1048573" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1048574" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1048575" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1048576" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
   </sheetData>
+  <autoFilter ref="A1:Q5"/>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
@@ -674,5 +726,6 @@
     <oddHeader/>
     <oddFooter/>
   </headerFooter>
+  <drawing r:id="rId1"/>
 </worksheet>
 </file>
--- a/Code/Jupiter/Connect4/Selected EVAL_PPO_results.xlsx
+++ b/Code/Jupiter/Connect4/Selected EVAL_PPO_results.xlsx
@@ -216,7 +216,7 @@
       <charset val="238"/>
     </font>
   </fonts>
-  <fills count="11">
+  <fills count="12">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -277,6 +277,12 @@
         <bgColor rgb="FF800080"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFA6A6"/>
+        <bgColor rgb="FFFF8080"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="2">
     <border diagonalUp="false" diagonalDown="false">
@@ -319,7 +325,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="29">
+  <cellXfs count="30">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -429,6 +435,10 @@
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="164" fontId="0" fillId="10" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="11" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -445,7 +455,7 @@
     <cellStyle name="Currency [0]" xfId="18" builtinId="7"/>
     <cellStyle name="Percent" xfId="19" builtinId="5"/>
   </cellStyles>
-  <dxfs count="21">
+  <dxfs count="22">
     <dxf>
       <fill>
         <patternFill patternType="solid">
@@ -482,6 +492,14 @@
       <fill>
         <patternFill patternType="solid">
           <fgColor rgb="FFFF8000"/>
+          <bgColor rgb="FF000000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFA6A6"/>
           <bgColor rgb="FF000000"/>
         </patternFill>
       </fill>
@@ -697,7 +715,7 @@
       <rgbColor rgb="FFCCFFCC"/>
       <rgbColor rgb="FFFFFF99"/>
       <rgbColor rgb="FF99CCFF"/>
-      <rgbColor rgb="FFFF99CC"/>
+      <rgbColor rgb="FFFFA6A6"/>
       <rgbColor rgb="FFCC99FF"/>
       <rgbColor rgb="FFFFCCCC"/>
       <rgbColor rgb="FF3366FF"/>
@@ -2084,8 +2102,8 @@
       <c r="A16" s="27" t="s">
         <v>39</v>
       </c>
-      <c r="B16" s="26" t="n">
-        <v>2</v>
+      <c r="B16" s="23" t="n">
+        <v>3</v>
       </c>
       <c r="C16" s="1" t="n">
         <v>0</v>
@@ -2163,7 +2181,7 @@
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A17" s="20" t="s">
+      <c r="A17" s="28" t="s">
         <v>40</v>
       </c>
       <c r="B17" s="23" t="n">
@@ -2248,7 +2266,7 @@
       <c r="B18" s="23" t="n">
         <v>99</v>
       </c>
-      <c r="C18" s="28" t="n">
+      <c r="C18" s="29" t="n">
         <v>0</v>
       </c>
       <c r="D18" s="3" t="n">
@@ -2327,7 +2345,7 @@
       <c r="B19" s="23" t="n">
         <v>99</v>
       </c>
-      <c r="C19" s="28" t="n">
+      <c r="C19" s="29" t="n">
         <v>0</v>
       </c>
       <c r="D19" s="3" t="n">
@@ -2470,108 +2488,108 @@
   </sheetData>
   <autoFilter ref="A2:Y19"/>
   <conditionalFormatting sqref="G1">
-    <cfRule type="cellIs" priority="2" operator="lessThan" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="14">
+    <cfRule type="cellIs" priority="2" operator="lessThan" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="15">
       <formula>1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E9:P12 E3:P7">
-    <cfRule type="cellIs" priority="3" operator="equal" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="15">
+    <cfRule type="cellIs" priority="3" operator="equal" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="16">
       <formula>1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="S1:S7 S9:S1048576">
-    <cfRule type="cellIs" priority="4" operator="greaterThan" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="15">
+    <cfRule type="cellIs" priority="4" operator="greaterThan" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="16">
       <formula>1100</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E9:P1048576 E1:P7">
-    <cfRule type="cellIs" priority="5" operator="lessThan" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="16">
+    <cfRule type="cellIs" priority="5" operator="lessThan" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="17">
       <formula>0.5</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="T1:T1048576">
-    <cfRule type="cellIs" priority="6" operator="greaterThan" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="17">
+    <cfRule type="cellIs" priority="6" operator="greaterThan" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="18">
       <formula>800</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="Q9:Q1048576 Q1:Q7">
-    <cfRule type="cellIs" priority="7" operator="greaterThan" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="17">
+    <cfRule type="cellIs" priority="7" operator="greaterThan" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="18">
       <formula>0.75</formula>
     </cfRule>
-    <cfRule type="cellIs" priority="8" operator="lessThan" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="18">
+    <cfRule type="cellIs" priority="8" operator="lessThan" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="19">
       <formula>0.6</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="X1:Y1 W9:W1048576 W1:W7">
-    <cfRule type="cellIs" priority="9" operator="greaterThan" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="17">
+    <cfRule type="cellIs" priority="9" operator="greaterThan" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="18">
       <formula>600</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="U1:U1048576">
-    <cfRule type="cellIs" priority="10" operator="greaterThan" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="17">
+    <cfRule type="cellIs" priority="10" operator="greaterThan" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="18">
       <formula>0.55</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="V1:V1048576">
-    <cfRule type="cellIs" priority="11" operator="greaterThan" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="17">
+    <cfRule type="cellIs" priority="11" operator="greaterThan" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="18">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="R12:R1048576 R1:R7 R9:R10">
-    <cfRule type="cellIs" priority="12" operator="greaterThan" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="19">
+    <cfRule type="cellIs" priority="12" operator="greaterThan" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="20">
       <formula>0.45</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="Y1 X1:X1048576">
-    <cfRule type="cellIs" priority="13" operator="greaterThan" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="19">
+    <cfRule type="cellIs" priority="13" operator="greaterThan" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="20">
       <formula>100</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="Y1:Y1048576">
-    <cfRule type="cellIs" priority="14" operator="greaterThan" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="19">
+    <cfRule type="cellIs" priority="14" operator="greaterThan" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="20">
       <formula>0.5</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E8:P8">
-    <cfRule type="cellIs" priority="15" operator="equal" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="15">
+    <cfRule type="cellIs" priority="15" operator="equal" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="16">
       <formula>1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="S8">
-    <cfRule type="cellIs" priority="16" operator="greaterThan" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="15">
+    <cfRule type="cellIs" priority="16" operator="greaterThan" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="16">
       <formula>1100</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E8:P8">
-    <cfRule type="cellIs" priority="17" operator="lessThan" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="16">
+    <cfRule type="cellIs" priority="17" operator="lessThan" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="17">
       <formula>0.5</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="Q8">
-    <cfRule type="cellIs" priority="18" operator="greaterThan" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="17">
+    <cfRule type="cellIs" priority="18" operator="greaterThan" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="18">
       <formula>0.75</formula>
     </cfRule>
-    <cfRule type="cellIs" priority="19" operator="lessThan" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="18">
+    <cfRule type="cellIs" priority="19" operator="lessThan" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="19">
       <formula>0.6</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="W8">
-    <cfRule type="cellIs" priority="20" operator="greaterThan" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="17">
+    <cfRule type="cellIs" priority="20" operator="greaterThan" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="18">
       <formula>600</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="R8">
-    <cfRule type="cellIs" priority="21" operator="greaterThan" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="19">
+    <cfRule type="cellIs" priority="21" operator="greaterThan" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="20">
       <formula>0.45</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="R11">
-    <cfRule type="cellIs" priority="22" operator="greaterThan" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="19">
+    <cfRule type="cellIs" priority="22" operator="greaterThan" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="20">
       <formula>0.45</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E1:P1048576">
-    <cfRule type="cellIs" priority="23" operator="greaterThan" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="20">
+    <cfRule type="cellIs" priority="23" operator="greaterThan" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="21">
       <formula>0.5</formula>
     </cfRule>
   </conditionalFormatting>

--- a/Code/Jupiter/Connect4/Selected EVAL_PPO_results.xlsx
+++ b/Code/Jupiter/Connect4/Selected EVAL_PPO_results.xlsx
@@ -10,10 +10,12 @@
   <sheets>
     <sheet name="Main" sheetId="1" state="visible" r:id="rId3"/>
     <sheet name="Bases" sheetId="2" state="visible" r:id="rId4"/>
+    <sheet name="Extended evals" sheetId="3" state="visible" r:id="rId5"/>
   </sheets>
   <definedNames>
     <definedName function="false" hidden="true" localSheetId="1" name="_xlnm._FilterDatabase" vbProcedure="false">Bases!$A$1:$Y$5</definedName>
-    <definedName function="false" hidden="true" localSheetId="0" name="_xlnm._FilterDatabase" vbProcedure="false">Main!$A$2:$Y$5</definedName>
+    <definedName function="false" hidden="true" localSheetId="2" name="_xlnm._FilterDatabase" vbProcedure="false">'Extended evals'!$A$2:$W$7</definedName>
+    <definedName function="false" hidden="true" localSheetId="0" name="_xlnm._FilterDatabase" vbProcedure="false">Main!$A$2:$Z$7</definedName>
   </definedNames>
   <calcPr iterateCount="100" refMode="A1" iterate="false" iterateDelta="0.0001"/>
   <extLst>
@@ -25,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="59" uniqueCount="34">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="89" uniqueCount="42">
   <si>
     <t xml:space="preserve">max</t>
   </si>
@@ -105,16 +107,22 @@
     <t xml:space="preserve">R</t>
   </si>
   <si>
+    <t xml:space="preserve">KaggleHyb</t>
+  </si>
+  <si>
     <t xml:space="preserve">PPO_1004</t>
   </si>
   <si>
-    <t xml:space="preserve">PPO_859</t>
-  </si>
-  <si>
-    <t xml:space="preserve">PPO_1005</t>
-  </si>
-  <si>
-    <t xml:space="preserve">PPO_926</t>
+    <t xml:space="preserve">PPO_2001</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PPO_2003</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PPO_2002</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PPO_2004</t>
   </si>
   <si>
     <t xml:space="preserve">BASE_10</t>
@@ -127,6 +135,24 @@
   </si>
   <si>
     <t xml:space="preserve">BASE_8</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tr</t>
+  </si>
+  <si>
+    <t xml:space="preserve">LA-8</t>
+  </si>
+  <si>
+    <t xml:space="preserve">LA-10</t>
+  </si>
+  <si>
+    <t xml:space="preserve">LA-12</t>
+  </si>
+  <si>
+    <t xml:space="preserve">LA-14</t>
+  </si>
+  <si>
+    <t xml:space="preserve">LA-15</t>
   </si>
 </sst>
 </file>
@@ -136,11 +162,11 @@
   <numFmts count="5">
     <numFmt numFmtId="164" formatCode="General"/>
     <numFmt numFmtId="165" formatCode="0"/>
-    <numFmt numFmtId="166" formatCode="0.000"/>
-    <numFmt numFmtId="167" formatCode="0.0"/>
+    <numFmt numFmtId="166" formatCode="0.0"/>
+    <numFmt numFmtId="167" formatCode="0.000"/>
     <numFmt numFmtId="168" formatCode="0.00"/>
   </numFmts>
-  <fonts count="7">
+  <fonts count="12">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -176,6 +202,21 @@
     </font>
     <font>
       <b val="true"/>
+      <sz val="9"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <charset val="238"/>
+    </font>
+    <font>
+      <sz val="8"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <charset val="238"/>
+    </font>
+    <font>
+      <b val="true"/>
       <sz val="6"/>
       <color theme="1"/>
       <name val="Calibri"/>
@@ -190,8 +231,32 @@
       <family val="2"/>
       <charset val="238"/>
     </font>
+    <font>
+      <b val="true"/>
+      <sz val="8"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <charset val="1"/>
+    </font>
+    <font>
+      <b val="true"/>
+      <sz val="6"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <charset val="1"/>
+    </font>
+    <font>
+      <b val="true"/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <charset val="1"/>
+    </font>
   </fonts>
-  <fills count="11">
+  <fills count="12">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -242,6 +307,12 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FFFFD7D7"/>
+        <bgColor rgb="FFFFCCCC"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FFFFBF00"/>
         <bgColor rgb="FFACB20C"/>
       </patternFill>
@@ -294,7 +365,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="26">
+  <cellXfs count="40">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -319,47 +390,55 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
     <xf numFmtId="164" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
+    <xf numFmtId="165" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="166" fontId="5" fillId="2" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="167" fontId="5" fillId="2" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
     <xf numFmtId="165" fontId="5" fillId="2" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="166" fontId="6" fillId="2" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="167" fontId="6" fillId="2" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="165" fontId="6" fillId="2" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="164" fontId="4" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="5" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="165" fontId="7" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="166" fontId="6" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="166" fontId="8" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="167" fontId="6" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="167" fontId="8" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="166" fontId="0" fillId="4" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="167" fontId="0" fillId="4" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="6" fillId="3" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="165" fontId="8" fillId="3" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -367,7 +446,7 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="167" fontId="0" fillId="5" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="166" fontId="0" fillId="5" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -379,7 +458,19 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="166" fontId="0" fillId="8" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="167" fontId="0" fillId="8" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="165" fontId="0" fillId="3" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="9" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="165" fontId="0" fillId="10" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -387,15 +478,51 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="0" fillId="9" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="0" fillId="11" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="10" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="165" fontId="0" fillId="11" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="0" fillId="10" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="167" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="167" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="167" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="10" fillId="4" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="167" fontId="9" fillId="4" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="9" fillId="4" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="11" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="167" fontId="11" fillId="4" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="4" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -408,7 +535,7 @@
     <cellStyle name="Currency [0]" xfId="18" builtinId="7"/>
     <cellStyle name="Percent" xfId="19" builtinId="5"/>
   </cellStyles>
-  <dxfs count="23">
+  <dxfs count="24">
     <dxf>
       <fill>
         <patternFill patternType="solid">
@@ -428,15 +555,7 @@
     <dxf>
       <fill>
         <patternFill patternType="solid">
-          <fgColor rgb="FFDEE6EF"/>
-          <bgColor rgb="FF000000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFFF00"/>
+          <fgColor rgb="FFFFD7D7"/>
           <bgColor rgb="FF000000"/>
         </patternFill>
       </fill>
@@ -499,22 +618,15 @@
     <dxf>
       <fill>
         <patternFill patternType="solid">
-          <fgColor rgb="FFACB20C"/>
+          <fgColor rgb="FFFFFF00"/>
           <bgColor rgb="FF000000"/>
         </patternFill>
       </fill>
     </dxf>
     <dxf>
-      <font>
-        <name val="Calibri"/>
-        <charset val="238"/>
-        <family val="2"/>
-        <b val="1"/>
-        <color rgb="FFFFFFFF"/>
-        <sz val="11"/>
-      </font>
       <fill>
-        <patternFill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFACB20C"/>
           <bgColor rgb="FF000000"/>
         </patternFill>
       </fill>
@@ -618,6 +730,21 @@
       </fill>
     </dxf>
     <dxf>
+      <font>
+        <name val="Calibri"/>
+        <charset val="238"/>
+        <family val="2"/>
+        <color rgb="FF006600"/>
+        <sz val="11"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFCCFFCC"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+    </dxf>
+    <dxf>
       <fill>
         <patternFill patternType="solid">
           <fgColor rgb="FFFF8000"/>
@@ -641,6 +768,21 @@
         </patternFill>
       </fill>
     </dxf>
+    <dxf>
+      <font>
+        <name val="Calibri"/>
+        <charset val="238"/>
+        <family val="2"/>
+        <color rgb="FFCC0000"/>
+        <sz val="11"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFCCCC"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+    </dxf>
   </dxfs>
   <colors>
     <indexedColors>
@@ -662,7 +804,7 @@
       <rgbColor rgb="FF808080"/>
       <rgbColor rgb="FF729FCF"/>
       <rgbColor rgb="FF993366"/>
-      <rgbColor rgb="FFFFFFCC"/>
+      <rgbColor rgb="FFFFD7D7"/>
       <rgbColor rgb="FFDEE6EF"/>
       <rgbColor rgb="FF660066"/>
       <rgbColor rgb="FFFF8080"/>
@@ -710,6 +852,10 @@
 </file>
 
 <file path=xl/drawings/drawing2.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships"/>
+</file>
+
+<file path=xl/drawings/drawing3.xml><?xml version="1.0" encoding="utf-8"?>
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships"/>
 </file>
 
@@ -824,213 +970,221 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:Y1048576"/>
+  <dimension ref="A1:Z1048576"/>
   <sheetFormatPr defaultColWidth="8.453125" defaultRowHeight="15" customHeight="true" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="17.47"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="2" width="7.37"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="7.91"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="3" width="10.83"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="4" width="10.57"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="4" width="8.84"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="4" width="7.82"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="4" width="9.46"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="4" width="8.19"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10" min="10" style="4" width="8.64"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="11" min="11" style="4" width="7.73"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="12" min="12" style="4" width="9.92"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="13" min="13" style="4" width="9.46"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="14" min="14" style="4" width="9.01"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="15" min="15" style="4" width="9.64"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="16" min="16" style="4" width="8.55"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="17" min="17" style="3" width="10.83"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="18" min="18" style="3" width="10.1"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="5.18"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="3" width="8.91"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="3" width="10.57"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="3" width="8.84"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="3" width="7.82"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="3" width="9.46"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="3" width="8.19"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10" min="10" style="3" width="8.64"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="11" min="11" style="3" width="7.73"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="12" min="12" style="3" width="9.92"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="13" min="13" style="3" width="9.46"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="14" min="14" style="3" width="9.01"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="15" min="15" style="3" width="9.64"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="16" min="16" style="3" width="8.55"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="17" min="17" style="4" width="10.83"/>
+    <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="18" min="18" style="4" width="8.46"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="19" min="19" style="2" width="8.37"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="20" min="20" style="2" width="9.64"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="21" min="21" style="5" width="12.92"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="22" min="22" style="4" width="13.01"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="22" min="22" style="3" width="13.01"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="23" min="23" style="2" width="10.73"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="24" min="24" style="1" width="12.55"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="25" min="25" style="3" width="11.83"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="25" min="25" style="4" width="11.83"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="26" min="26" style="6" width="11.83"/>
   </cols>
   <sheetData>
-    <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="6" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="7"/>
-      <c r="C1" s="7"/>
-      <c r="D1" s="8" t="n">
-        <f aca="false">MAX(D3:D4)</f>
-        <v>1</v>
-      </c>
-      <c r="E1" s="8" t="n">
-        <f aca="false">MAX(E3:E4)</f>
-        <v>1</v>
-      </c>
-      <c r="F1" s="8" t="n">
-        <f aca="false">MAX(F3:F4)</f>
-        <v>1</v>
-      </c>
-      <c r="G1" s="8" t="n">
-        <f aca="false">MAX(G3:G4)</f>
-        <v>1</v>
-      </c>
-      <c r="H1" s="8" t="n">
-        <f aca="false">MAX(H3:H4)</f>
-        <v>1</v>
-      </c>
-      <c r="I1" s="8" t="n">
-        <f aca="false">MAX(I3:I4)</f>
-        <v>1</v>
-      </c>
-      <c r="J1" s="8" t="n">
-        <f aca="false">MAX(J3:J4)</f>
-        <v>1</v>
-      </c>
-      <c r="K1" s="8" t="n">
-        <f aca="false">MAX(K3:K4)</f>
-        <v>1</v>
-      </c>
-      <c r="L1" s="8" t="n">
-        <f aca="false">MAX(L3:L4)</f>
-        <v>1</v>
-      </c>
-      <c r="M1" s="8" t="n">
-        <f aca="false">MAX(M3:M4)</f>
-        <v>1</v>
-      </c>
-      <c r="N1" s="8" t="n">
-        <f aca="false">MAX(N3:N4)</f>
-        <v>1</v>
-      </c>
-      <c r="O1" s="8" t="n">
-        <f aca="false">MAX(O3:O4)</f>
-        <v>1</v>
-      </c>
-      <c r="P1" s="8" t="n">
-        <f aca="false">MAX(P3:P4)</f>
-        <v>1</v>
-      </c>
-      <c r="Q1" s="8" t="n">
-        <f aca="false">MAX(Q3:Q4)</f>
-        <v>1</v>
-      </c>
-      <c r="R1" s="8" t="n">
-        <f aca="false">MAX(R3:R4)</f>
-        <v>0.524</v>
-      </c>
-      <c r="S1" s="8" t="n">
-        <f aca="false">MAX(S3:S4)</f>
+    <row r="1" s="12" customFormat="true" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1" s="7" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="8"/>
+      <c r="C1" s="8"/>
+      <c r="D1" s="9" t="n">
+        <f aca="false">MAX(D3:D40)</f>
+        <v>1</v>
+      </c>
+      <c r="E1" s="9" t="n">
+        <f aca="false">MAX(E3:E40)</f>
+        <v>1</v>
+      </c>
+      <c r="F1" s="9" t="n">
+        <f aca="false">MAX(F3:F40)</f>
+        <v>1</v>
+      </c>
+      <c r="G1" s="9" t="n">
+        <f aca="false">MAX(G3:G40)</f>
+        <v>1</v>
+      </c>
+      <c r="H1" s="9" t="n">
+        <f aca="false">MAX(H3:H40)</f>
+        <v>1</v>
+      </c>
+      <c r="I1" s="9" t="n">
+        <f aca="false">MAX(I3:I40)</f>
+        <v>1</v>
+      </c>
+      <c r="J1" s="9" t="n">
+        <f aca="false">MAX(J3:J40)</f>
+        <v>1</v>
+      </c>
+      <c r="K1" s="9" t="n">
+        <f aca="false">MAX(K3:K40)</f>
+        <v>1</v>
+      </c>
+      <c r="L1" s="9" t="n">
+        <f aca="false">MAX(L3:L40)</f>
+        <v>1</v>
+      </c>
+      <c r="M1" s="9" t="n">
+        <f aca="false">MAX(M3:M40)</f>
+        <v>1</v>
+      </c>
+      <c r="N1" s="9" t="n">
+        <f aca="false">MAX(N3:N40)</f>
+        <v>1</v>
+      </c>
+      <c r="O1" s="9" t="n">
+        <f aca="false">MAX(O3:O40)</f>
+        <v>1</v>
+      </c>
+      <c r="P1" s="9" t="n">
+        <f aca="false">MAX(P3:P40)</f>
+        <v>1</v>
+      </c>
+      <c r="Q1" s="10" t="n">
+        <f aca="false">MAX(Q3:Q40)</f>
+        <v>1</v>
+      </c>
+      <c r="R1" s="10" t="n">
+        <f aca="false">MAX(R3:R40)</f>
+        <v>0.563</v>
+      </c>
+      <c r="S1" s="11" t="n">
+        <f aca="false">MAX(S3:S40)</f>
         <v>1367.670305</v>
       </c>
-      <c r="T1" s="8" t="n">
-        <f aca="false">MAX(T3:T4)</f>
+      <c r="T1" s="11" t="n">
+        <f aca="false">MAX(T3:T40)</f>
         <v>1367.670305</v>
       </c>
-      <c r="U1" s="8" t="n">
-        <f aca="false">MAX(U3:U4)</f>
-        <v>0.762</v>
-      </c>
-      <c r="V1" s="9" t="n">
-        <f aca="false">MAX(V3:V4)</f>
+      <c r="U1" s="10" t="n">
+        <f aca="false">MAX(U3:U40)</f>
+        <v>0.781471739102527</v>
+      </c>
+      <c r="V1" s="11" t="n">
+        <f aca="false">MAX(V3:V40)</f>
         <v>1000</v>
       </c>
-      <c r="W1" s="10" t="n">
-        <f aca="false">MAX(W3:W4)</f>
-        <v>725</v>
-      </c>
-      <c r="X1" s="10" t="n">
-        <f aca="false">MAX(X3:X4)</f>
-        <v>524</v>
-      </c>
-      <c r="Y1" s="8" t="n">
-        <f aca="false">MAX(Y3:Y4)</f>
-        <v>0.524</v>
+      <c r="W1" s="11" t="n">
+        <f aca="false">MAX(W3:W40)</f>
+        <v>743</v>
+      </c>
+      <c r="X1" s="11" t="n">
+        <f aca="false">MAX(X3:X40)</f>
+        <v>562</v>
+      </c>
+      <c r="Y1" s="10" t="n">
+        <f aca="false">MAX(Y3:Y40)</f>
+        <v>0.56303182356928</v>
+      </c>
+      <c r="Z1" s="10" t="n">
+        <f aca="false">MAX(Z3:Z40)</f>
+        <v>0</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="11" t="s">
-        <v>1</v>
-      </c>
-      <c r="B2" s="12" t="s">
+      <c r="A2" s="13" t="s">
+        <v>1</v>
+      </c>
+      <c r="B2" s="14" t="s">
         <v>2</v>
       </c>
-      <c r="C2" s="12" t="s">
+      <c r="C2" s="14" t="s">
         <v>3</v>
       </c>
-      <c r="D2" s="13" t="s">
+      <c r="D2" s="15" t="s">
         <v>4</v>
       </c>
-      <c r="E2" s="14" t="s">
+      <c r="E2" s="15" t="s">
         <v>5</v>
       </c>
-      <c r="F2" s="14" t="s">
+      <c r="F2" s="15" t="s">
         <v>6</v>
       </c>
-      <c r="G2" s="14" t="s">
+      <c r="G2" s="15" t="s">
         <v>7</v>
       </c>
-      <c r="H2" s="14" t="s">
+      <c r="H2" s="15" t="s">
         <v>8</v>
       </c>
-      <c r="I2" s="14" t="s">
+      <c r="I2" s="15" t="s">
         <v>9</v>
       </c>
-      <c r="J2" s="14" t="s">
+      <c r="J2" s="15" t="s">
         <v>10</v>
       </c>
-      <c r="K2" s="14" t="s">
+      <c r="K2" s="15" t="s">
         <v>11</v>
       </c>
-      <c r="L2" s="14" t="s">
+      <c r="L2" s="15" t="s">
         <v>12</v>
       </c>
-      <c r="M2" s="14" t="s">
+      <c r="M2" s="15" t="s">
         <v>13</v>
       </c>
-      <c r="N2" s="14" t="s">
+      <c r="N2" s="15" t="s">
         <v>14</v>
       </c>
-      <c r="O2" s="14" t="s">
+      <c r="O2" s="15" t="s">
         <v>15</v>
       </c>
-      <c r="P2" s="14" t="s">
+      <c r="P2" s="15" t="s">
         <v>16</v>
       </c>
-      <c r="Q2" s="13" t="s">
+      <c r="Q2" s="16" t="s">
         <v>17</v>
       </c>
-      <c r="R2" s="15" t="s">
+      <c r="R2" s="17" t="s">
         <v>18</v>
       </c>
-      <c r="S2" s="16" t="s">
+      <c r="S2" s="18" t="s">
         <v>19</v>
       </c>
-      <c r="T2" s="16" t="s">
+      <c r="T2" s="18" t="s">
         <v>20</v>
       </c>
-      <c r="U2" s="17" t="s">
+      <c r="U2" s="19" t="s">
         <v>21</v>
       </c>
-      <c r="V2" s="18" t="s">
+      <c r="V2" s="20" t="s">
         <v>22</v>
       </c>
-      <c r="W2" s="19" t="s">
+      <c r="W2" s="21" t="s">
         <v>23</v>
       </c>
-      <c r="X2" s="20" t="s">
+      <c r="X2" s="22" t="s">
         <v>24</v>
       </c>
-      <c r="Y2" s="21" t="s">
+      <c r="Y2" s="23" t="s">
         <v>25</v>
+      </c>
+      <c r="Z2" s="24" t="s">
+        <v>26</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A3" s="22" t="s">
-        <v>26</v>
-      </c>
-      <c r="B3" s="23" t="n">
+      <c r="A3" s="25" t="s">
+        <v>27</v>
+      </c>
+      <c r="B3" s="26" t="n">
         <v>1</v>
       </c>
       <c r="C3" s="1" t="n">
@@ -1039,46 +1193,46 @@
       <c r="D3" s="3" t="n">
         <v>1</v>
       </c>
-      <c r="E3" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="F3" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="G3" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="H3" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="I3" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="J3" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="K3" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="L3" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="M3" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="N3" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="O3" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="P3" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="Q3" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="R3" s="3" t="n">
+      <c r="E3" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="F3" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="G3" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="H3" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="I3" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="J3" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="K3" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="L3" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="M3" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="N3" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="O3" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="P3" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q3" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="R3" s="4" t="n">
         <v>0.524</v>
       </c>
       <c r="S3" s="2" t="n">
@@ -1092,27 +1246,27 @@
         <f aca="false">AVERAGE(Q3, R3)</f>
         <v>0.762</v>
       </c>
-      <c r="V3" s="4" t="n">
+      <c r="V3" s="3" t="n">
         <f aca="false">D3*E3*F3*G3*H3*I3*J3*K3*L3*M3*N3*O3*P3*1000</f>
         <v>1000</v>
       </c>
       <c r="W3" s="1" t="n">
-        <v>725</v>
-      </c>
-      <c r="X3" s="4" t="n">
+        <v>731</v>
+      </c>
+      <c r="X3" s="3" t="n">
         <f aca="false">V3*Q3*R3</f>
         <v>524</v>
       </c>
-      <c r="Y3" s="3" t="n">
+      <c r="Y3" s="4" t="n">
         <f aca="false">R3/Q3</f>
         <v>0.524</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A4" s="20" t="s">
-        <v>27</v>
-      </c>
-      <c r="B4" s="23" t="n">
+      <c r="A4" s="27" t="s">
+        <v>28</v>
+      </c>
+      <c r="B4" s="26" t="n">
         <v>1</v>
       </c>
       <c r="C4" s="1" t="n">
@@ -1121,302 +1275,392 @@
       <c r="D4" s="3" t="n">
         <v>1</v>
       </c>
-      <c r="E4" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="F4" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="G4" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="H4" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="I4" s="4" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="J4" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="K4" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="L4" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="M4" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="N4" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="O4" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="P4" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="Q4" s="3" t="n">
-        <v>0.992245209733209</v>
-      </c>
-      <c r="R4" s="3" t="n">
-        <v>0.412</v>
+      <c r="E4" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="F4" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="G4" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="H4" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="I4" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="J4" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="K4" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="L4" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="M4" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="N4" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="O4" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="P4" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q4" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="R4" s="4" t="n">
+        <v>0.562</v>
       </c>
       <c r="S4" s="2" t="n">
-        <v>1161.870481</v>
+        <v>1354.375858</v>
       </c>
       <c r="T4" s="2" t="n">
         <f aca="false">Q4*S4</f>
-        <v>1152.86041910267</v>
+        <v>1354.375858</v>
       </c>
       <c r="U4" s="5" t="n">
         <f aca="false">AVERAGE(Q4, R4)</f>
-        <v>0.702122604866605</v>
-      </c>
-      <c r="V4" s="4" t="n">
+        <v>0.781</v>
+      </c>
+      <c r="V4" s="3" t="n">
         <f aca="false">D4*E4*F4*G4*H4*I4*J4*K4*L4*M4*N4*O4*P4*1000</f>
-        <v>500</v>
-      </c>
-      <c r="X4" s="4" t="n">
+        <v>1000</v>
+      </c>
+      <c r="X4" s="3" t="n">
         <f aca="false">V4*Q4*R4</f>
-        <v>204.402513205041</v>
-      </c>
-      <c r="Y4" s="3" t="n">
+        <v>562</v>
+      </c>
+      <c r="Y4" s="4" t="n">
         <f aca="false">R4/Q4</f>
-        <v>0.415219943577029</v>
+        <v>0.562</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A5" s="20" t="s">
-        <v>28</v>
-      </c>
-      <c r="B5" s="23" t="n">
+      <c r="A5" s="27" t="s">
+        <v>29</v>
+      </c>
+      <c r="B5" s="26" t="n">
         <v>1</v>
       </c>
       <c r="C5" s="1" t="n">
         <v>0</v>
       </c>
       <c r="D5" s="3" t="n">
-        <v>0.99</v>
-      </c>
-      <c r="E5" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="F5" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="G5" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="H5" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="I5" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="J5" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="K5" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="L5" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="M5" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="N5" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="O5" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="P5" s="4" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="Q5" s="3" t="n">
-        <v>0.775632559901853</v>
-      </c>
-      <c r="R5" s="3" t="n">
-        <v>0.346</v>
+        <v>1</v>
+      </c>
+      <c r="E5" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="F5" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="G5" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="H5" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="I5" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="J5" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="K5" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="L5" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="M5" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="N5" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="O5" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="P5" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q5" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="R5" s="4" t="n">
+        <v>0.509</v>
       </c>
       <c r="S5" s="2" t="n">
-        <v>1287.815</v>
+        <v>1337.197942</v>
       </c>
       <c r="T5" s="2" t="n">
         <f aca="false">Q5*S5</f>
-        <v>998.871245130005</v>
+        <v>1337.197942</v>
       </c>
       <c r="U5" s="5" t="n">
         <f aca="false">AVERAGE(Q5, R5)</f>
-        <v>0.560816279950926</v>
-      </c>
-      <c r="V5" s="4" t="n">
+        <v>0.7545</v>
+      </c>
+      <c r="V5" s="3" t="n">
         <f aca="false">D5*E5*F5*G5*H5*I5*J5*K5*L5*M5*N5*O5*P5*1000</f>
-        <v>495</v>
-      </c>
-      <c r="X5" s="4" t="n">
+        <v>1000</v>
+      </c>
+      <c r="X5" s="3" t="n">
         <f aca="false">V5*Q5*R5</f>
-        <v>132.84258853439</v>
-      </c>
-      <c r="Y5" s="3" t="n">
+        <v>509</v>
+      </c>
+      <c r="Y5" s="4" t="n">
         <f aca="false">R5/Q5</f>
-        <v>0.446087513453254</v>
+        <v>0.509</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A6" s="20" t="s">
-        <v>29</v>
-      </c>
-      <c r="B6" s="23" t="n">
+      <c r="A6" s="25" t="s">
+        <v>30</v>
+      </c>
+      <c r="B6" s="26" t="n">
         <v>1</v>
       </c>
       <c r="C6" s="1" t="n">
         <v>0</v>
       </c>
       <c r="D6" s="3" t="n">
-        <v>0.98</v>
-      </c>
-      <c r="E6" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="F6" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="G6" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="H6" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="I6" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="J6" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="K6" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="L6" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="M6" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="N6" s="4" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="O6" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="P6" s="4" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="Q6" s="3" t="n">
-        <v>0.71718606562065</v>
-      </c>
-      <c r="R6" s="3" t="n">
-        <v>0.307</v>
+        <v>0.99</v>
+      </c>
+      <c r="E6" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="F6" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="G6" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="H6" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="I6" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="J6" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="K6" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="L6" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="M6" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="N6" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="O6" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="P6" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q6" s="4" t="n">
+        <v>0.999943478205053</v>
+      </c>
+      <c r="R6" s="4" t="n">
+        <v>0.563</v>
       </c>
       <c r="S6" s="2" t="n">
-        <v>1109.295154</v>
+        <v>1329.146493</v>
       </c>
       <c r="T6" s="2" t="n">
         <f aca="false">Q6*S6</f>
-        <v>795.571027109313</v>
+        <v>1329.07136725447</v>
       </c>
       <c r="U6" s="5" t="n">
         <f aca="false">AVERAGE(Q6, R6)</f>
-        <v>0.512093032810325</v>
-      </c>
-      <c r="V6" s="4" t="n">
+        <v>0.781471739102527</v>
+      </c>
+      <c r="V6" s="3" t="n">
         <f aca="false">D6*E6*F6*G6*H6*I6*J6*K6*L6*M6*N6*O6*P6*1000</f>
-        <v>245</v>
-      </c>
-      <c r="X6" s="4" t="n">
+        <v>990</v>
+      </c>
+      <c r="W6" s="2" t="n">
+        <v>734</v>
+      </c>
+      <c r="X6" s="3" t="n">
         <f aca="false">V6*Q6*R6</f>
-        <v>53.9431499256572</v>
-      </c>
-      <c r="Y6" s="3" t="n">
+        <v>557.33849644715</v>
+      </c>
+      <c r="Y6" s="4" t="n">
         <f aca="false">R6/Q6</f>
-        <v>0.428061858304962</v>
+        <v>0.56303182356928</v>
       </c>
     </row>
-    <row r="1048576" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A7" s="27" t="s">
+        <v>31</v>
+      </c>
+      <c r="B7" s="26" t="n">
+        <v>2</v>
+      </c>
+      <c r="C7" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="D7" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="E7" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="F7" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="G7" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="H7" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="I7" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="J7" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="K7" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="L7" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="M7" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="N7" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="O7" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="P7" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q7" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="R7" s="4" t="n">
+        <v>0.496</v>
+      </c>
+      <c r="S7" s="2" t="n">
+        <v>1316.05153</v>
+      </c>
+      <c r="T7" s="2" t="n">
+        <f aca="false">Q7*S7</f>
+        <v>1316.05153</v>
+      </c>
+      <c r="U7" s="5" t="n">
+        <f aca="false">AVERAGE(Q7, R7)</f>
+        <v>0.748</v>
+      </c>
+      <c r="V7" s="3" t="n">
+        <f aca="false">D7*E7*F7*G7*H7*I7*J7*K7*L7*M7*N7*O7*P7*1000</f>
+        <v>1000</v>
+      </c>
+      <c r="W7" s="2" t="n">
+        <v>743</v>
+      </c>
+      <c r="X7" s="3" t="n">
+        <f aca="false">V7*Q7*R7</f>
+        <v>496</v>
+      </c>
+      <c r="Y7" s="4" t="n">
+        <f aca="false">R7/Q7</f>
+        <v>0.496</v>
+      </c>
+    </row>
+    <row r="1048576" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
   </sheetData>
-  <autoFilter ref="A2:Y5"/>
-  <conditionalFormatting sqref="G1">
-    <cfRule type="cellIs" priority="2" operator="lessThan" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="12">
+  <autoFilter ref="A2:Z7"/>
+  <conditionalFormatting sqref="E3:P4">
+    <cfRule type="cellIs" priority="2" operator="equal" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="12">
       <formula>1</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="E3:P4">
-    <cfRule type="cellIs" priority="3" operator="equal" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="13">
-      <formula>1</formula>
+  <conditionalFormatting sqref="S5:S1048576 S2:S3">
+    <cfRule type="cellIs" priority="3" operator="greaterThan" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="12">
+      <formula>1100</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="S1:S1048576">
-    <cfRule type="cellIs" priority="4" operator="greaterThan" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="13">
+  <conditionalFormatting sqref="E2:P1048576">
+    <cfRule type="cellIs" priority="4" operator="lessThan" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="13">
+      <formula>0.5</formula>
+    </cfRule>
+    <cfRule type="cellIs" priority="5" operator="greaterThan" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="14">
+      <formula>0.5</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="T8:T1048576 T2:T4">
+    <cfRule type="cellIs" priority="6" operator="greaterThan" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="15">
+      <formula>800</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="Q2:Q1048576">
+    <cfRule type="cellIs" priority="7" operator="greaterThan" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="15">
+      <formula>0.75</formula>
+    </cfRule>
+    <cfRule type="cellIs" priority="8" operator="lessThan" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="16">
+      <formula>0.6</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="W2:W1048576">
+    <cfRule type="cellIs" priority="9" operator="greaterThan" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="15">
+      <formula>600</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="U2:U1048576">
+    <cfRule type="cellIs" priority="10" operator="greaterThanOrEqual" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="15">
+      <formula>0.55</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="V2:V1048576">
+    <cfRule type="cellIs" priority="11" operator="greaterThan" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="15">
+      <formula>0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="X2:X1048576">
+    <cfRule type="cellIs" priority="12" operator="greaterThan" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="17">
+      <formula>100</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="Y2:Y1048576">
+    <cfRule type="cellIs" priority="13" operator="greaterThan" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="17">
+      <formula>0.5</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="T5:T7">
+    <cfRule type="cellIs" priority="14" operator="greaterThan" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="15">
+      <formula>800</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="R2:R1048576">
+    <cfRule type="cellIs" priority="15" operator="greaterThan" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="18">
+      <formula>0.45</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="S4">
+    <cfRule type="cellIs" priority="16" operator="greaterThan" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="12">
       <formula>1100</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="E1:P1048576">
-    <cfRule type="cellIs" priority="5" operator="lessThan" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="14">
-      <formula>0.5</formula>
-    </cfRule>
-    <cfRule type="cellIs" priority="6" operator="greaterThan" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="15">
-      <formula>0.5</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="T7:T1048576 T1:T4">
-    <cfRule type="cellIs" priority="7" operator="greaterThan" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="16">
+  <conditionalFormatting sqref="Z2:Z1048576">
+    <cfRule type="cellIs" priority="17" operator="greaterThan" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="19">
       <formula>800</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="Q1:Q1048576">
-    <cfRule type="cellIs" priority="8" operator="greaterThan" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="16">
-      <formula>0.75</formula>
-    </cfRule>
-    <cfRule type="cellIs" priority="9" operator="lessThan" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="17">
-      <formula>0.6</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="X1:Y1 W1:W1048576">
-    <cfRule type="cellIs" priority="10" operator="greaterThan" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="16">
-      <formula>600</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="U1:U1048576">
-    <cfRule type="cellIs" priority="11" operator="greaterThan" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="16">
-      <formula>0.55</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="V1:V1048576">
-    <cfRule type="cellIs" priority="12" operator="greaterThan" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="16">
-      <formula>0</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="Y1 X1:X1048576">
-    <cfRule type="cellIs" priority="13" operator="greaterThan" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="18">
-      <formula>100</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="Y1:Y1048576">
-    <cfRule type="cellIs" priority="14" operator="greaterThan" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="18">
-      <formula>0.5</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="T5:T6">
-    <cfRule type="cellIs" priority="15" operator="greaterThan" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="16">
-      <formula>800</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="R1:R1048576">
-    <cfRule type="cellIs" priority="16" operator="greaterThan" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="19">
-      <formula>0.45</formula>
     </cfRule>
   </conditionalFormatting>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
@@ -1441,160 +1685,160 @@
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="17.47"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="2" width="7.37"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="7.91"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="3" width="10.83"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="4" width="10.57"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="4" width="8.84"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="4" width="7.82"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="4" width="9.46"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="4" width="8.19"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10" min="10" style="4" width="8.64"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="11" min="11" style="4" width="7.73"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="12" min="12" style="4" width="9.92"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="13" min="13" style="4" width="9.46"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="14" min="14" style="4" width="9.01"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="15" min="15" style="4" width="9.64"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="16" min="16" style="4" width="8.55"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="17" min="17" style="3" width="10.83"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="18" min="18" style="3" width="10.1"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="4" width="10.83"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="3" width="10.57"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="3" width="8.84"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="3" width="7.82"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="3" width="9.46"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="3" width="8.19"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10" min="10" style="3" width="8.64"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="11" min="11" style="3" width="7.73"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="12" min="12" style="3" width="9.92"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="13" min="13" style="3" width="9.46"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="14" min="14" style="3" width="9.01"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="15" min="15" style="3" width="9.64"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="16" min="16" style="3" width="8.55"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="17" min="17" style="4" width="10.83"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="18" min="18" style="4" width="10.1"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="19" min="19" style="2" width="8.37"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="20" min="20" style="2" width="9.64"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="21" min="21" style="5" width="12.92"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="22" min="22" style="4" width="13.01"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="22" min="22" style="3" width="13.01"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="23" min="23" style="2" width="10.73"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="24" min="24" style="1" width="12.55"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="25" min="25" style="3" width="11.83"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="25" min="25" style="4" width="11.83"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="11" t="s">
-        <v>1</v>
-      </c>
-      <c r="B1" s="12" t="s">
+      <c r="A1" s="13" t="s">
+        <v>1</v>
+      </c>
+      <c r="B1" s="14" t="s">
         <v>2</v>
       </c>
-      <c r="C1" s="12" t="s">
+      <c r="C1" s="14" t="s">
         <v>3</v>
       </c>
-      <c r="D1" s="13" t="s">
+      <c r="D1" s="16" t="s">
         <v>4</v>
       </c>
-      <c r="E1" s="14" t="s">
+      <c r="E1" s="15" t="s">
         <v>5</v>
       </c>
-      <c r="F1" s="14" t="s">
+      <c r="F1" s="15" t="s">
         <v>6</v>
       </c>
-      <c r="G1" s="14" t="s">
+      <c r="G1" s="15" t="s">
         <v>7</v>
       </c>
-      <c r="H1" s="14" t="s">
+      <c r="H1" s="15" t="s">
         <v>8</v>
       </c>
-      <c r="I1" s="14" t="s">
+      <c r="I1" s="15" t="s">
         <v>9</v>
       </c>
-      <c r="J1" s="14" t="s">
+      <c r="J1" s="15" t="s">
         <v>10</v>
       </c>
-      <c r="K1" s="14" t="s">
+      <c r="K1" s="15" t="s">
         <v>11</v>
       </c>
-      <c r="L1" s="14" t="s">
+      <c r="L1" s="15" t="s">
         <v>12</v>
       </c>
-      <c r="M1" s="14" t="s">
+      <c r="M1" s="15" t="s">
         <v>13</v>
       </c>
-      <c r="N1" s="14" t="s">
+      <c r="N1" s="15" t="s">
         <v>14</v>
       </c>
-      <c r="O1" s="14" t="s">
+      <c r="O1" s="15" t="s">
         <v>15</v>
       </c>
-      <c r="P1" s="14" t="s">
+      <c r="P1" s="15" t="s">
         <v>16</v>
       </c>
-      <c r="Q1" s="13" t="s">
+      <c r="Q1" s="16" t="s">
         <v>17</v>
       </c>
-      <c r="R1" s="15" t="s">
+      <c r="R1" s="17" t="s">
         <v>18</v>
       </c>
-      <c r="S1" s="16" t="s">
+      <c r="S1" s="18" t="s">
         <v>19</v>
       </c>
-      <c r="T1" s="16" t="s">
+      <c r="T1" s="18" t="s">
         <v>20</v>
       </c>
-      <c r="U1" s="17" t="s">
+      <c r="U1" s="19" t="s">
         <v>21</v>
       </c>
-      <c r="V1" s="18" t="s">
+      <c r="V1" s="20" t="s">
         <v>22</v>
       </c>
-      <c r="W1" s="19" t="s">
+      <c r="W1" s="21" t="s">
         <v>23</v>
       </c>
-      <c r="X1" s="20" t="s">
+      <c r="X1" s="22" t="s">
         <v>24</v>
       </c>
-      <c r="Y1" s="21" t="s">
+      <c r="Y1" s="23" t="s">
         <v>25</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A2" s="24" t="s">
-        <v>30</v>
-      </c>
-      <c r="B2" s="25" t="n">
+      <c r="A2" s="28" t="s">
+        <v>32</v>
+      </c>
+      <c r="B2" s="29" t="n">
         <v>99</v>
       </c>
       <c r="C2" s="1" t="n">
         <v>0</v>
       </c>
-      <c r="D2" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="E2" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="F2" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="G2" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="H2" s="4" t="n">
+      <c r="D2" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="E2" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="F2" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="G2" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="H2" s="3" t="n">
         <v>0.5</v>
       </c>
-      <c r="I2" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="J2" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="K2" s="4" t="n">
+      <c r="I2" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="J2" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="K2" s="3" t="n">
         <v>0.5</v>
       </c>
-      <c r="L2" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="M2" s="4" t="n">
+      <c r="L2" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="M2" s="3" t="n">
         <v>0.5</v>
       </c>
-      <c r="N2" s="4" t="n">
+      <c r="N2" s="3" t="n">
         <v>0.5</v>
       </c>
-      <c r="O2" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="P2" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q2" s="3" t="n">
+      <c r="O2" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="P2" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q2" s="4" t="n">
         <v>0.213570171644556</v>
       </c>
-      <c r="R2" s="3" t="n">
+      <c r="R2" s="4" t="n">
         <v>0.212</v>
       </c>
       <c r="S2" s="2" t="n">
@@ -1608,72 +1852,72 @@
         <f aca="false">AVERAGE(Q2, R2)</f>
         <v>0.212785085822278</v>
       </c>
-      <c r="V2" s="4" t="n">
+      <c r="V2" s="3" t="n">
         <f aca="false">D2*E2*F2*G2*H2*I2*J2*K2*L2*M2*N2*O2*P2*1000</f>
         <v>0</v>
       </c>
-      <c r="X2" s="4" t="n">
+      <c r="X2" s="3" t="n">
         <f aca="false">V2*Q2*R2</f>
         <v>0</v>
       </c>
-      <c r="Y2" s="3" t="n">
+      <c r="Y2" s="4" t="n">
         <f aca="false">R2/Q2</f>
         <v>0.992647982475899</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A3" s="24" t="s">
-        <v>31</v>
-      </c>
-      <c r="B3" s="25" t="n">
+      <c r="A3" s="28" t="s">
+        <v>33</v>
+      </c>
+      <c r="B3" s="29" t="n">
         <v>99</v>
       </c>
       <c r="C3" s="1" t="n">
         <v>0</v>
       </c>
-      <c r="D3" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="E3" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="F3" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="G3" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="H3" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="I3" s="4" t="n">
+      <c r="D3" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="E3" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="F3" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="G3" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="H3" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="I3" s="3" t="n">
         <v>0.5</v>
       </c>
-      <c r="J3" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="K3" s="4" t="n">
+      <c r="J3" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="K3" s="3" t="n">
         <v>0.5</v>
       </c>
-      <c r="L3" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="M3" s="4" t="n">
+      <c r="L3" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="M3" s="3" t="n">
         <v>0.5</v>
       </c>
-      <c r="N3" s="4" t="n">
+      <c r="N3" s="3" t="n">
         <v>0.5</v>
       </c>
-      <c r="O3" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="P3" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q3" s="3" t="n">
+      <c r="O3" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="P3" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q3" s="4" t="n">
         <v>0.211354517282616</v>
       </c>
-      <c r="R3" s="3" t="n">
+      <c r="R3" s="4" t="n">
         <v>0.15</v>
       </c>
       <c r="S3" s="2" t="n">
@@ -1687,22 +1931,22 @@
         <f aca="false">AVERAGE(Q3, R3)</f>
         <v>0.180677258641308</v>
       </c>
-      <c r="V3" s="4" t="n">
+      <c r="V3" s="3" t="n">
         <f aca="false">D3*E3*F3*G3*H3*I3*J3*K3*L3*M3*N3*O3*P3*1000</f>
         <v>0</v>
       </c>
-      <c r="X3" s="4" t="n">
+      <c r="X3" s="3" t="n">
         <f aca="false">V3*Q3*R3</f>
         <v>0</v>
       </c>
-      <c r="Y3" s="3" t="n">
+      <c r="Y3" s="4" t="n">
         <f aca="false">R3/Q3</f>
         <v>0.709708039026321</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="1" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="B4" s="2" t="n">
         <v>0.018735</v>
@@ -1710,49 +1954,49 @@
       <c r="C4" s="1" t="n">
         <v>0</v>
       </c>
-      <c r="D4" s="3" t="n">
+      <c r="D4" s="4" t="n">
         <v>0.99</v>
       </c>
-      <c r="E4" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="F4" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="G4" s="4" t="n">
+      <c r="E4" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="F4" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="G4" s="3" t="n">
         <v>0.5</v>
       </c>
-      <c r="H4" s="4" t="n">
+      <c r="H4" s="3" t="n">
         <v>0.5</v>
       </c>
-      <c r="I4" s="4" t="n">
+      <c r="I4" s="3" t="n">
         <v>0.5</v>
       </c>
-      <c r="J4" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="K4" s="4" t="n">
+      <c r="J4" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="K4" s="3" t="n">
         <v>0.5</v>
       </c>
-      <c r="L4" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="M4" s="4" t="n">
+      <c r="L4" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="M4" s="3" t="n">
         <v>0.5</v>
       </c>
-      <c r="N4" s="4" t="n">
+      <c r="N4" s="3" t="n">
         <v>0.5</v>
       </c>
-      <c r="O4" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="P4" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q4" s="3" t="n">
+      <c r="O4" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="P4" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q4" s="4" t="n">
         <v>0.201802333936495</v>
       </c>
-      <c r="R4" s="3" t="n">
+      <c r="R4" s="4" t="n">
         <v>0.187</v>
       </c>
       <c r="S4" s="2" t="n">
@@ -1766,72 +2010,72 @@
         <f aca="false">AVERAGE(Q4, R4)</f>
         <v>0.194401166968248</v>
       </c>
-      <c r="V4" s="4" t="n">
+      <c r="V4" s="3" t="n">
         <f aca="false">D4*E4*F4*G4*H4*I4*J4*K4*L4*M4*N4*O4*P4*1000</f>
         <v>0</v>
       </c>
-      <c r="X4" s="4" t="n">
+      <c r="X4" s="3" t="n">
         <f aca="false">V4*Q4*R4</f>
         <v>0</v>
       </c>
-      <c r="Y4" s="3" t="n">
+      <c r="Y4" s="4" t="n">
         <f aca="false">R4/Q4</f>
         <v>0.926649342216463</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A5" s="24" t="s">
-        <v>33</v>
-      </c>
-      <c r="B5" s="25" t="n">
+      <c r="A5" s="28" t="s">
+        <v>35</v>
+      </c>
+      <c r="B5" s="29" t="n">
         <v>99</v>
       </c>
       <c r="C5" s="1" t="n">
         <v>0</v>
       </c>
-      <c r="D5" s="3" t="n">
+      <c r="D5" s="4" t="n">
         <v>0.995</v>
       </c>
-      <c r="E5" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="F5" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="G5" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="H5" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="I5" s="4" t="n">
+      <c r="E5" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="F5" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="G5" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="H5" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="I5" s="3" t="n">
         <v>0.5</v>
       </c>
-      <c r="J5" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="K5" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L5" s="4" t="n">
+      <c r="J5" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="K5" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="L5" s="3" t="n">
         <v>0.5</v>
       </c>
-      <c r="M5" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="N5" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="O5" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="P5" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q5" s="3" t="n">
+      <c r="M5" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="N5" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="O5" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="P5" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q5" s="4" t="n">
         <v>0.0866669481949934</v>
       </c>
-      <c r="R5" s="3" t="n">
+      <c r="R5" s="4" t="n">
         <v>0.179</v>
       </c>
       <c r="S5" s="2" t="n">
@@ -1845,15 +2089,15 @@
         <f aca="false">AVERAGE(Q5, R5)</f>
         <v>0.132833474097497</v>
       </c>
-      <c r="V5" s="4" t="n">
+      <c r="V5" s="3" t="n">
         <f aca="false">D5*E5*F5*G5*H5*I5*J5*K5*L5*M5*N5*O5*P5*1000</f>
         <v>0</v>
       </c>
-      <c r="X5" s="4" t="n">
+      <c r="X5" s="3" t="n">
         <f aca="false">V5*Q5*R5</f>
         <v>0</v>
       </c>
-      <c r="Y5" s="3" t="n">
+      <c r="Y5" s="4" t="n">
         <f aca="false">R5/Q5</f>
         <v>2.06537790620324</v>
       </c>
@@ -1947,58 +2191,58 @@
   </sheetData>
   <autoFilter ref="A1:Y5"/>
   <conditionalFormatting sqref="S1:S1048576">
-    <cfRule type="cellIs" priority="2" operator="greaterThan" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="13">
+    <cfRule type="cellIs" priority="2" operator="greaterThan" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="12">
       <formula>1100</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E1:P1048576">
-    <cfRule type="cellIs" priority="3" operator="lessThan" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="14">
+    <cfRule type="cellIs" priority="3" operator="lessThan" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="13">
       <formula>0.5</formula>
     </cfRule>
-    <cfRule type="cellIs" priority="4" operator="greaterThan" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="15">
+    <cfRule type="cellIs" priority="4" operator="greaterThan" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="14">
       <formula>0.5</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="T1:T1048576">
-    <cfRule type="cellIs" priority="5" operator="greaterThan" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="16">
+    <cfRule type="cellIs" priority="5" operator="greaterThan" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="15">
       <formula>800</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="Q1:Q1048576">
-    <cfRule type="cellIs" priority="6" operator="greaterThan" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="16">
+    <cfRule type="cellIs" priority="6" operator="greaterThan" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="15">
       <formula>0.75</formula>
     </cfRule>
-    <cfRule type="cellIs" priority="7" operator="lessThan" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="17">
+    <cfRule type="cellIs" priority="7" operator="lessThan" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="16">
       <formula>0.6</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="W1:W1048576">
-    <cfRule type="cellIs" priority="8" operator="greaterThan" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="16">
+    <cfRule type="cellIs" priority="8" operator="greaterThan" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="15">
       <formula>600</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="U1:U1048576">
-    <cfRule type="cellIs" priority="9" operator="greaterThan" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="16">
+    <cfRule type="cellIs" priority="9" operator="greaterThan" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="15">
       <formula>0.55</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="V1:V1048576">
-    <cfRule type="cellIs" priority="10" operator="greaterThan" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="16">
+    <cfRule type="cellIs" priority="10" operator="greaterThan" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="15">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="R1:R1048576">
-    <cfRule type="cellIs" priority="11" operator="greaterThan" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="18">
+    <cfRule type="cellIs" priority="11" operator="greaterThan" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="17">
       <formula>0.45</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="X1:X1048576">
-    <cfRule type="cellIs" priority="12" operator="greaterThan" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="18">
+    <cfRule type="cellIs" priority="12" operator="greaterThan" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="17">
       <formula>100</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="Y1:Y1048576">
-    <cfRule type="cellIs" priority="13" operator="greaterThan" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="18">
+    <cfRule type="cellIs" priority="13" operator="greaterThan" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="17">
       <formula>0.5</formula>
     </cfRule>
   </conditionalFormatting>
@@ -2011,4 +2255,549 @@
   </headerFooter>
   <drawing r:id="rId1"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+  <sheetPr filterMode="false">
+    <pageSetUpPr fitToPage="false"/>
+  </sheetPr>
+  <dimension ref="A1:W7"/>
+  <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="13.8" customHeight="true" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <cols>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="30" width="6.82"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="12" width="5.73"/>
+    <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="22" min="22" style="31" width="11.53"/>
+  </cols>
+  <sheetData>
+    <row r="1" s="12" customFormat="true" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1" s="32"/>
+      <c r="B1" s="33"/>
+      <c r="C1" s="32"/>
+      <c r="D1" s="32" t="n">
+        <f aca="false">MAX(D3:D40)</f>
+        <v>1</v>
+      </c>
+      <c r="E1" s="32" t="n">
+        <f aca="false">MAX(E3:E40)</f>
+        <v>1</v>
+      </c>
+      <c r="F1" s="32" t="n">
+        <f aca="false">MAX(F3:F40)</f>
+        <v>1</v>
+      </c>
+      <c r="G1" s="32" t="n">
+        <f aca="false">MAX(G3:G40)</f>
+        <v>1</v>
+      </c>
+      <c r="H1" s="32" t="n">
+        <f aca="false">MAX(H3:H40)</f>
+        <v>1</v>
+      </c>
+      <c r="I1" s="32" t="n">
+        <f aca="false">MAX(I3:I40)</f>
+        <v>1</v>
+      </c>
+      <c r="J1" s="32" t="n">
+        <f aca="false">MAX(J3:J40)</f>
+        <v>1</v>
+      </c>
+      <c r="K1" s="32" t="n">
+        <f aca="false">MAX(K3:K40)</f>
+        <v>1</v>
+      </c>
+      <c r="L1" s="32" t="n">
+        <f aca="false">MAX(L3:L40)</f>
+        <v>1</v>
+      </c>
+      <c r="M1" s="32" t="n">
+        <f aca="false">MAX(M3:M40)</f>
+        <v>1</v>
+      </c>
+      <c r="N1" s="32" t="n">
+        <f aca="false">MAX(N3:N40)</f>
+        <v>1</v>
+      </c>
+      <c r="O1" s="32" t="n">
+        <f aca="false">MAX(O3:O40)</f>
+        <v>1</v>
+      </c>
+      <c r="P1" s="32" t="n">
+        <f aca="false">MAX(P3:P40)</f>
+        <v>1</v>
+      </c>
+      <c r="Q1" s="32" t="n">
+        <f aca="false">MAX(Q3:Q40)</f>
+        <v>1</v>
+      </c>
+      <c r="R1" s="32" t="n">
+        <f aca="false">MAX(R3:R40)</f>
+        <v>0</v>
+      </c>
+      <c r="S1" s="32" t="n">
+        <f aca="false">MAX(S3:S40)</f>
+        <v>1</v>
+      </c>
+      <c r="T1" s="32" t="n">
+        <f aca="false">MAX(T3:T40)</f>
+        <v>0</v>
+      </c>
+      <c r="U1" s="32" t="n">
+        <f aca="false">MAX(U3:U40)</f>
+        <v>0.5</v>
+      </c>
+      <c r="V1" s="33" t="n">
+        <f aca="false">MAX(V3:V40)</f>
+        <v>0.54852335453657</v>
+      </c>
+    </row>
+    <row r="2" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A2" s="34" t="s">
+        <v>1</v>
+      </c>
+      <c r="B2" s="35" t="s">
+        <v>36</v>
+      </c>
+      <c r="C2" s="36" t="s">
+        <v>3</v>
+      </c>
+      <c r="D2" s="37" t="s">
+        <v>4</v>
+      </c>
+      <c r="E2" s="37" t="s">
+        <v>5</v>
+      </c>
+      <c r="F2" s="37" t="s">
+        <v>6</v>
+      </c>
+      <c r="G2" s="37" t="s">
+        <v>7</v>
+      </c>
+      <c r="H2" s="37" t="s">
+        <v>8</v>
+      </c>
+      <c r="I2" s="37" t="s">
+        <v>9</v>
+      </c>
+      <c r="J2" s="37" t="s">
+        <v>10</v>
+      </c>
+      <c r="K2" s="37" t="s">
+        <v>11</v>
+      </c>
+      <c r="L2" s="37" t="s">
+        <v>12</v>
+      </c>
+      <c r="M2" s="37" t="s">
+        <v>13</v>
+      </c>
+      <c r="N2" s="37" t="s">
+        <v>37</v>
+      </c>
+      <c r="O2" s="37" t="s">
+        <v>14</v>
+      </c>
+      <c r="P2" s="37" t="s">
+        <v>38</v>
+      </c>
+      <c r="Q2" s="37" t="s">
+        <v>15</v>
+      </c>
+      <c r="R2" s="37" t="s">
+        <v>39</v>
+      </c>
+      <c r="S2" s="37" t="s">
+        <v>16</v>
+      </c>
+      <c r="T2" s="37" t="s">
+        <v>40</v>
+      </c>
+      <c r="U2" s="37" t="s">
+        <v>41</v>
+      </c>
+      <c r="V2" s="38" t="s">
+        <v>17</v>
+      </c>
+      <c r="W2" s="21" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="3" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A3" s="39" t="s">
+        <v>29</v>
+      </c>
+      <c r="B3" s="30" t="n">
+        <v>0.132811</v>
+      </c>
+      <c r="C3" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="D3" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="E3" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="F3" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="G3" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="H3" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="I3" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="J3" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="K3" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="L3" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="M3" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="N3" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="O3" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="P3" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q3" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="R3" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="S3" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="T3" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="U3" s="0" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="V3" s="31" t="n">
+        <v>0.54852335453657</v>
+      </c>
+    </row>
+    <row r="4" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A4" s="39" t="s">
+        <v>31</v>
+      </c>
+      <c r="B4" s="30" t="n">
+        <v>0.132316</v>
+      </c>
+      <c r="C4" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="D4" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="E4" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="F4" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="G4" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="H4" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="I4" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="J4" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="K4" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="L4" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="M4" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="N4" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="O4" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="P4" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q4" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="R4" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="S4" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="T4" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="U4" s="0" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="V4" s="31" t="n">
+        <v>0.54852335453657</v>
+      </c>
+      <c r="W4" s="6" t="n">
+        <f aca="false">Main!W7</f>
+        <v>743</v>
+      </c>
+    </row>
+    <row r="5" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A5" s="0" t="s">
+        <v>28</v>
+      </c>
+      <c r="B5" s="30" t="n">
+        <v>0.132271</v>
+      </c>
+      <c r="C5" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="D5" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="E5" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="F5" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="G5" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="H5" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="I5" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="J5" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="K5" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="L5" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="M5" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="N5" s="0" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="O5" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="P5" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q5" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="R5" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="S5" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="T5" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="U5" s="0" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="V5" s="31" t="n">
+        <v>0.534958826011471</v>
+      </c>
+    </row>
+    <row r="6" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A6" s="0" t="s">
+        <v>27</v>
+      </c>
+      <c r="B6" s="30" t="n">
+        <v>0.133852</v>
+      </c>
+      <c r="C6" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="D6" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="E6" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="F6" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="G6" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="H6" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="I6" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="J6" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="K6" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="L6" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="M6" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="N6" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="O6" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="P6" s="0" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="Q6" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="R6" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="S6" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="T6" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="U6" s="0" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="V6" s="31" t="n">
+        <v>0.521936878627375</v>
+      </c>
+      <c r="W6" s="0" t="n">
+        <f aca="false">Main!W3</f>
+        <v>731</v>
+      </c>
+    </row>
+    <row r="7" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A7" s="0" t="s">
+        <v>30</v>
+      </c>
+      <c r="B7" s="30" t="n">
+        <v>0.132477</v>
+      </c>
+      <c r="C7" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="D7" s="0" t="n">
+        <v>0.99</v>
+      </c>
+      <c r="E7" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="F7" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="G7" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="H7" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="I7" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="J7" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="K7" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="L7" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="M7" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="N7" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="O7" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="P7" s="0" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="Q7" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="R7" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="S7" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="T7" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="U7" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="V7" s="31" t="n">
+        <v>0.378930047686369</v>
+      </c>
+      <c r="W7" s="6" t="n">
+        <f aca="false">Main!W6</f>
+        <v>734</v>
+      </c>
+    </row>
+  </sheetData>
+  <autoFilter ref="A2:W7"/>
+  <conditionalFormatting sqref="D1:U1048576">
+    <cfRule type="cellIs" priority="2" operator="greaterThan" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="19">
+      <formula>0.5</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="D1:U1048576">
+    <cfRule type="cellIs" priority="3" operator="lessThan" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="23">
+      <formula>0.5</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="W2">
+    <cfRule type="cellIs" priority="4" operator="greaterThan" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="15">
+      <formula>600</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
+  <pageMargins left="0.7875" right="0.7875" top="1.05277777777778" bottom="1.05277777777778" header="0.7875" footer="0.7875"/>
+  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <headerFooter differentFirst="false" differentOddEven="false">
+    <oddHeader>&amp;C&amp;"Times New Roman,Navadno"&amp;12&amp;Kffffff&amp;A</oddHeader>
+    <oddFooter>&amp;C&amp;"Times New Roman,Navadno"&amp;12&amp;KffffffPage &amp;P</oddFooter>
+  </headerFooter>
+  <drawing r:id="rId1"/>
+</worksheet>
 </file>
--- a/Code/Jupiter/Connect4/Selected EVAL_PPO_results.xlsx
+++ b/Code/Jupiter/Connect4/Selected EVAL_PPO_results.xlsx
@@ -5,17 +5,23 @@
   <workbookPr backupFile="false" showObjects="all" date1904="false"/>
   <workbookProtection/>
   <bookViews>
-    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="0"/>
+    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="5"/>
   </bookViews>
   <sheets>
     <sheet name="Main" sheetId="1" state="visible" r:id="rId3"/>
     <sheet name="Bases" sheetId="2" state="visible" r:id="rId4"/>
     <sheet name="Extended evals" sheetId="3" state="visible" r:id="rId5"/>
+    <sheet name="Hybrid" sheetId="4" state="visible" r:id="rId6"/>
+    <sheet name="Hybrid_2" sheetId="5" state="visible" r:id="rId7"/>
+    <sheet name="PPO_2004_LA13_20" sheetId="6" state="visible" r:id="rId8"/>
   </sheets>
   <definedNames>
     <definedName function="false" hidden="true" localSheetId="1" name="_xlnm._FilterDatabase" vbProcedure="false">Bases!$A$1:$Y$5</definedName>
     <definedName function="false" hidden="true" localSheetId="2" name="_xlnm._FilterDatabase" vbProcedure="false">'Extended evals'!$A$2:$W$7</definedName>
+    <definedName function="false" hidden="true" localSheetId="3" name="_xlnm._FilterDatabase" vbProcedure="false">Hybrid!$A$1:$D$31</definedName>
+    <definedName function="false" hidden="true" localSheetId="4" name="_xlnm._FilterDatabase" vbProcedure="false">Hybrid_2!$A$1:$F$2</definedName>
     <definedName function="false" hidden="true" localSheetId="0" name="_xlnm._FilterDatabase" vbProcedure="false">Main!$A$2:$Z$7</definedName>
+    <definedName function="false" hidden="true" localSheetId="5" name="_xlnm._FilterDatabase" vbProcedure="false">PPO_2004_LA13_20!$A$1:$D$3</definedName>
   </definedNames>
   <calcPr iterateCount="100" refMode="A1" iterate="false" iterateDelta="0.0001"/>
   <extLst>
@@ -27,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="89" uniqueCount="42">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="105" uniqueCount="50">
   <si>
     <t xml:space="preserve">max</t>
   </si>
@@ -110,21 +116,21 @@
     <t xml:space="preserve">KaggleHyb</t>
   </si>
   <si>
+    <t xml:space="preserve">PPO_2004</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PPO_2003</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PPO_2002</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PPO_2001</t>
+  </si>
+  <si>
     <t xml:space="preserve">PPO_1004</t>
   </si>
   <si>
-    <t xml:space="preserve">PPO_2001</t>
-  </si>
-  <si>
-    <t xml:space="preserve">PPO_2003</t>
-  </si>
-  <si>
-    <t xml:space="preserve">PPO_2002</t>
-  </si>
-  <si>
-    <t xml:space="preserve">PPO_2004</t>
-  </si>
-  <si>
     <t xml:space="preserve">BASE_10</t>
   </si>
   <si>
@@ -153,18 +159,43 @@
   </si>
   <si>
     <t xml:space="preserve">LA-15</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Model</t>
+  </si>
+  <si>
+    <t xml:space="preserve">depth</t>
+  </si>
+  <si>
+    <t xml:space="preserve">move</t>
+  </si>
+  <si>
+    <t xml:space="preserve">none, LA only</t>
+  </si>
+  <si>
+    <t xml:space="preserve">depth_odd</t>
+  </si>
+  <si>
+    <t xml:space="preserve">move_odd</t>
+  </si>
+  <si>
+    <t xml:space="preserve">depth_even</t>
+  </si>
+  <si>
+    <t xml:space="preserve">move_even</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="5">
+  <numFmts count="6">
     <numFmt numFmtId="164" formatCode="General"/>
     <numFmt numFmtId="165" formatCode="0"/>
     <numFmt numFmtId="166" formatCode="0.0"/>
     <numFmt numFmtId="167" formatCode="0.000"/>
     <numFmt numFmtId="168" formatCode="0.00"/>
+    <numFmt numFmtId="169" formatCode="#"/>
   </numFmts>
   <fonts count="12">
     <font>
@@ -209,13 +240,6 @@
       <charset val="238"/>
     </font>
     <font>
-      <sz val="8"/>
-      <color theme="1"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <charset val="238"/>
-    </font>
-    <font>
       <b val="true"/>
       <sz val="6"/>
       <color theme="1"/>
@@ -226,6 +250,13 @@
     <font>
       <b val="true"/>
       <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <charset val="238"/>
+    </font>
+    <font>
+      <sz val="8"/>
       <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
@@ -256,7 +287,7 @@
       <charset val="1"/>
     </font>
   </fonts>
-  <fills count="12">
+  <fills count="15">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -307,20 +338,38 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FFFFBF00"/>
+        <bgColor rgb="FFACB20C"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FFFFD7D7"/>
         <bgColor rgb="FFFFCCCC"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFBF00"/>
-        <bgColor rgb="FFACB20C"/>
+        <fgColor rgb="FFFF8000"/>
+        <bgColor rgb="FFFF6600"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFF8000"/>
-        <bgColor rgb="FFFF6600"/>
+        <fgColor rgb="FFAFD095"/>
+        <bgColor rgb="FF99CCFF"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE8F2A1"/>
+        <bgColor rgb="FFCCFFCC"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFFF"/>
+        <bgColor rgb="FFDEE6EF"/>
       </patternFill>
     </fill>
   </fills>
@@ -365,7 +414,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="40">
+  <cellXfs count="44">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -390,10 +439,6 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
     <xf numFmtId="164" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -414,23 +459,19 @@
       <alignment horizontal="center" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
     <xf numFmtId="164" fontId="4" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="7" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="165" fontId="6" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="166" fontId="8" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="166" fontId="7" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="167" fontId="8" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="167" fontId="7" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -438,7 +479,7 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="8" fillId="3" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="165" fontId="7" fillId="3" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -462,15 +503,7 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="0" fillId="3" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="9" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="165" fontId="0" fillId="10" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="165" fontId="0" fillId="3" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -478,6 +511,14 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
+    <xf numFmtId="165" fontId="0" fillId="9" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="10" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
     <xf numFmtId="164" fontId="0" fillId="11" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -486,43 +527,67 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="167" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="167" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="167" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="169" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="167" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="167" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="10" fillId="4" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="169" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="167" fontId="9" fillId="4" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="10" fillId="4" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="9" fillId="4" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="167" fontId="9" fillId="4" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="11" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="9" fillId="4" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="167" fontId="11" fillId="4" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="11" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="4" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="167" fontId="11" fillId="4" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="169" fontId="0" fillId="6" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="12" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="13" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="14" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -535,7 +600,7 @@
     <cellStyle name="Currency [0]" xfId="18" builtinId="7"/>
     <cellStyle name="Percent" xfId="19" builtinId="5"/>
   </cellStyles>
-  <dxfs count="24">
+  <dxfs count="27">
     <dxf>
       <fill>
         <patternFill patternType="solid">
@@ -556,6 +621,14 @@
       <fill>
         <patternFill patternType="solid">
           <fgColor rgb="FFFFD7D7"/>
+          <bgColor rgb="FF000000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFFF00"/>
           <bgColor rgb="FF000000"/>
         </patternFill>
       </fill>
@@ -618,86 +691,8 @@
     <dxf>
       <fill>
         <patternFill patternType="solid">
-          <fgColor rgb="FFFFFF00"/>
-          <bgColor rgb="FF000000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
           <fgColor rgb="FFACB20C"/>
           <bgColor rgb="FF000000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <name val="Calibri"/>
-        <charset val="238"/>
-        <family val="2"/>
-        <color rgb="FF006600"/>
-        <sz val="11"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFCCFFCC"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <name val="Calibri"/>
-        <charset val="238"/>
-        <family val="2"/>
-        <color rgb="FFCC0000"/>
-        <sz val="11"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFCCCC"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <name val="Calibri"/>
-        <charset val="238"/>
-        <family val="2"/>
-        <color rgb="FF006600"/>
-        <sz val="11"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFCCFFCC"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <name val="Calibri"/>
-        <charset val="238"/>
-        <family val="2"/>
-        <color rgb="FF006600"/>
-        <sz val="11"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFCCFFCC"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <name val="Calibri"/>
-        <charset val="238"/>
-        <family val="2"/>
-        <color rgb="FFCC0000"/>
-        <sz val="11"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFCCCC"/>
         </patternFill>
       </fill>
     </dxf>
@@ -742,7 +737,48 @@
           <bgColor rgb="FFCCFFCC"/>
         </patternFill>
       </fill>
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+    </dxf>
+    <dxf>
+      <font>
+        <name val="Calibri"/>
+        <charset val="238"/>
+        <family val="2"/>
+        <color rgb="FF006600"/>
+        <sz val="11"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFCCFFCC"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <name val="Calibri"/>
+        <charset val="238"/>
+        <family val="2"/>
+        <color rgb="FF006600"/>
+        <sz val="11"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFCCFFCC"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <name val="Calibri"/>
+        <charset val="238"/>
+        <family val="2"/>
+        <color rgb="FF006600"/>
+        <sz val="11"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFCCFFCC"/>
+        </patternFill>
+      </fill>
     </dxf>
     <dxf>
       <fill>
@@ -781,7 +817,58 @@
           <bgColor rgb="FFFFCCCC"/>
         </patternFill>
       </fill>
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+    </dxf>
+    <dxf>
+      <font>
+        <name val="Calibri"/>
+        <charset val="238"/>
+        <family val="2"/>
+        <color rgb="FFCC0000"/>
+        <sz val="11"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFCCCC"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <name val="Calibri"/>
+        <charset val="238"/>
+        <family val="2"/>
+        <color rgb="FFCC0000"/>
+        <sz val="11"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFCCCC"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFAFD095"/>
+          <bgColor rgb="FF000000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFE8F2A1"/>
+          <bgColor rgb="FF000000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFFFFF"/>
+          <bgColor rgb="FF000000"/>
+        </patternFill>
+      </fill>
     </dxf>
   </dxfs>
   <colors>
@@ -800,7 +887,7 @@
       <rgbColor rgb="FFACB20C"/>
       <rgbColor rgb="FF800080"/>
       <rgbColor rgb="FF008080"/>
-      <rgbColor rgb="FFC0C0C0"/>
+      <rgbColor rgb="FFAFD095"/>
       <rgbColor rgb="FF808080"/>
       <rgbColor rgb="FF729FCF"/>
       <rgbColor rgb="FF993366"/>
@@ -821,7 +908,7 @@
       <rgbColor rgb="FF00CCFF"/>
       <rgbColor rgb="FFCCFFFF"/>
       <rgbColor rgb="FFCCFFCC"/>
-      <rgbColor rgb="FFFFFF99"/>
+      <rgbColor rgb="FFE8F2A1"/>
       <rgbColor rgb="FF99CCFF"/>
       <rgbColor rgb="FFFF99CC"/>
       <rgbColor rgb="FFCC99FF"/>
@@ -856,6 +943,18 @@
 </file>
 
 <file path=xl/drawings/drawing3.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships"/>
+</file>
+
+<file path=xl/drawings/drawing4.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships"/>
+</file>
+
+<file path=xl/drawings/drawing5.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships"/>
+</file>
+
+<file path=xl/drawings/drawing6.xml><?xml version="1.0" encoding="utf-8"?>
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships"/>
 </file>
 
@@ -998,194 +1097,194 @@
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="23" min="23" style="2" width="10.73"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="24" min="24" style="1" width="12.55"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="25" min="25" style="4" width="11.83"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="26" min="26" style="6" width="11.83"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="26" min="26" style="2" width="11.83"/>
   </cols>
   <sheetData>
-    <row r="1" s="12" customFormat="true" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="7" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="8"/>
-      <c r="C1" s="8"/>
-      <c r="D1" s="9" t="n">
+    <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1" s="6" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="7"/>
+      <c r="C1" s="7"/>
+      <c r="D1" s="8" t="n">
         <f aca="false">MAX(D3:D40)</f>
         <v>1</v>
       </c>
-      <c r="E1" s="9" t="n">
+      <c r="E1" s="8" t="n">
         <f aca="false">MAX(E3:E40)</f>
         <v>1</v>
       </c>
-      <c r="F1" s="9" t="n">
+      <c r="F1" s="8" t="n">
         <f aca="false">MAX(F3:F40)</f>
         <v>1</v>
       </c>
-      <c r="G1" s="9" t="n">
+      <c r="G1" s="8" t="n">
         <f aca="false">MAX(G3:G40)</f>
         <v>1</v>
       </c>
-      <c r="H1" s="9" t="n">
+      <c r="H1" s="8" t="n">
         <f aca="false">MAX(H3:H40)</f>
         <v>1</v>
       </c>
-      <c r="I1" s="9" t="n">
+      <c r="I1" s="8" t="n">
         <f aca="false">MAX(I3:I40)</f>
         <v>1</v>
       </c>
-      <c r="J1" s="9" t="n">
+      <c r="J1" s="8" t="n">
         <f aca="false">MAX(J3:J40)</f>
         <v>1</v>
       </c>
-      <c r="K1" s="9" t="n">
+      <c r="K1" s="8" t="n">
         <f aca="false">MAX(K3:K40)</f>
         <v>1</v>
       </c>
-      <c r="L1" s="9" t="n">
+      <c r="L1" s="8" t="n">
         <f aca="false">MAX(L3:L40)</f>
         <v>1</v>
       </c>
-      <c r="M1" s="9" t="n">
+      <c r="M1" s="8" t="n">
         <f aca="false">MAX(M3:M40)</f>
         <v>1</v>
       </c>
-      <c r="N1" s="9" t="n">
+      <c r="N1" s="8" t="n">
         <f aca="false">MAX(N3:N40)</f>
         <v>1</v>
       </c>
-      <c r="O1" s="9" t="n">
+      <c r="O1" s="8" t="n">
         <f aca="false">MAX(O3:O40)</f>
         <v>1</v>
       </c>
-      <c r="P1" s="9" t="n">
+      <c r="P1" s="8" t="n">
         <f aca="false">MAX(P3:P40)</f>
         <v>1</v>
       </c>
-      <c r="Q1" s="10" t="n">
+      <c r="Q1" s="9" t="n">
         <f aca="false">MAX(Q3:Q40)</f>
         <v>1</v>
       </c>
-      <c r="R1" s="10" t="n">
+      <c r="R1" s="9" t="n">
         <f aca="false">MAX(R3:R40)</f>
         <v>0.563</v>
       </c>
-      <c r="S1" s="11" t="n">
+      <c r="S1" s="10" t="n">
         <f aca="false">MAX(S3:S40)</f>
         <v>1367.670305</v>
       </c>
-      <c r="T1" s="11" t="n">
+      <c r="T1" s="10" t="n">
         <f aca="false">MAX(T3:T40)</f>
         <v>1367.670305</v>
       </c>
-      <c r="U1" s="10" t="n">
+      <c r="U1" s="9" t="n">
         <f aca="false">MAX(U3:U40)</f>
         <v>0.781471739102527</v>
       </c>
-      <c r="V1" s="11" t="n">
+      <c r="V1" s="10" t="n">
         <f aca="false">MAX(V3:V40)</f>
         <v>1000</v>
       </c>
-      <c r="W1" s="11" t="n">
+      <c r="W1" s="10" t="n">
         <f aca="false">MAX(W3:W40)</f>
-        <v>743</v>
-      </c>
-      <c r="X1" s="11" t="n">
+        <v>739</v>
+      </c>
+      <c r="X1" s="10" t="n">
         <f aca="false">MAX(X3:X40)</f>
         <v>562</v>
       </c>
-      <c r="Y1" s="10" t="n">
+      <c r="Y1" s="9" t="n">
         <f aca="false">MAX(Y3:Y40)</f>
         <v>0.56303182356928</v>
       </c>
-      <c r="Z1" s="10" t="n">
+      <c r="Z1" s="9" t="n">
         <f aca="false">MAX(Z3:Z40)</f>
         <v>0</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="13" t="s">
-        <v>1</v>
-      </c>
-      <c r="B2" s="14" t="s">
+      <c r="A2" s="11" t="s">
+        <v>1</v>
+      </c>
+      <c r="B2" s="12" t="s">
         <v>2</v>
       </c>
-      <c r="C2" s="14" t="s">
+      <c r="C2" s="12" t="s">
         <v>3</v>
       </c>
-      <c r="D2" s="15" t="s">
+      <c r="D2" s="13" t="s">
         <v>4</v>
       </c>
-      <c r="E2" s="15" t="s">
+      <c r="E2" s="13" t="s">
         <v>5</v>
       </c>
-      <c r="F2" s="15" t="s">
+      <c r="F2" s="13" t="s">
         <v>6</v>
       </c>
-      <c r="G2" s="15" t="s">
+      <c r="G2" s="13" t="s">
         <v>7</v>
       </c>
-      <c r="H2" s="15" t="s">
+      <c r="H2" s="13" t="s">
         <v>8</v>
       </c>
-      <c r="I2" s="15" t="s">
+      <c r="I2" s="13" t="s">
         <v>9</v>
       </c>
-      <c r="J2" s="15" t="s">
+      <c r="J2" s="13" t="s">
         <v>10</v>
       </c>
-      <c r="K2" s="15" t="s">
+      <c r="K2" s="13" t="s">
         <v>11</v>
       </c>
-      <c r="L2" s="15" t="s">
+      <c r="L2" s="13" t="s">
         <v>12</v>
       </c>
-      <c r="M2" s="15" t="s">
+      <c r="M2" s="13" t="s">
         <v>13</v>
       </c>
-      <c r="N2" s="15" t="s">
+      <c r="N2" s="13" t="s">
         <v>14</v>
       </c>
-      <c r="O2" s="15" t="s">
+      <c r="O2" s="13" t="s">
         <v>15</v>
       </c>
-      <c r="P2" s="15" t="s">
+      <c r="P2" s="13" t="s">
         <v>16</v>
       </c>
-      <c r="Q2" s="16" t="s">
+      <c r="Q2" s="14" t="s">
         <v>17</v>
       </c>
-      <c r="R2" s="17" t="s">
+      <c r="R2" s="15" t="s">
         <v>18</v>
       </c>
-      <c r="S2" s="18" t="s">
+      <c r="S2" s="16" t="s">
         <v>19</v>
       </c>
-      <c r="T2" s="18" t="s">
+      <c r="T2" s="16" t="s">
         <v>20</v>
       </c>
-      <c r="U2" s="19" t="s">
+      <c r="U2" s="17" t="s">
         <v>21</v>
       </c>
-      <c r="V2" s="20" t="s">
+      <c r="V2" s="18" t="s">
         <v>22</v>
       </c>
-      <c r="W2" s="21" t="s">
+      <c r="W2" s="19" t="s">
         <v>23</v>
       </c>
-      <c r="X2" s="22" t="s">
+      <c r="X2" s="20" t="s">
         <v>24</v>
       </c>
-      <c r="Y2" s="23" t="s">
+      <c r="Y2" s="21" t="s">
         <v>25</v>
       </c>
-      <c r="Z2" s="24" t="s">
+      <c r="Z2" s="22" t="s">
         <v>26</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A3" s="25" t="s">
+      <c r="A3" s="23" t="s">
         <v>27</v>
       </c>
-      <c r="B3" s="26" t="n">
-        <v>1</v>
+      <c r="B3" s="24" t="n">
+        <v>2</v>
       </c>
       <c r="C3" s="1" t="n">
         <v>0</v>
@@ -1233,40 +1332,40 @@
         <v>1</v>
       </c>
       <c r="R3" s="4" t="n">
-        <v>0.524</v>
+        <v>0.496</v>
       </c>
       <c r="S3" s="2" t="n">
-        <v>1367.670305</v>
+        <v>1316.05153</v>
       </c>
       <c r="T3" s="2" t="n">
         <f aca="false">Q3*S3</f>
-        <v>1367.670305</v>
+        <v>1316.05153</v>
       </c>
       <c r="U3" s="5" t="n">
         <f aca="false">AVERAGE(Q3, R3)</f>
-        <v>0.762</v>
+        <v>0.748</v>
       </c>
       <c r="V3" s="3" t="n">
         <f aca="false">D3*E3*F3*G3*H3*I3*J3*K3*L3*M3*N3*O3*P3*1000</f>
         <v>1000</v>
       </c>
-      <c r="W3" s="1" t="n">
+      <c r="W3" s="2" t="n">
         <v>731</v>
       </c>
       <c r="X3" s="3" t="n">
         <f aca="false">V3*Q3*R3</f>
-        <v>524</v>
+        <v>496</v>
       </c>
       <c r="Y3" s="4" t="n">
         <f aca="false">R3/Q3</f>
-        <v>0.524</v>
+        <v>0.496</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A4" s="27" t="s">
+      <c r="A4" s="20" t="s">
         <v>28</v>
       </c>
-      <c r="B4" s="26" t="n">
+      <c r="B4" s="24" t="n">
         <v>1</v>
       </c>
       <c r="C4" s="1" t="n">
@@ -1315,44 +1414,47 @@
         <v>1</v>
       </c>
       <c r="R4" s="4" t="n">
-        <v>0.562</v>
+        <v>0.509</v>
       </c>
       <c r="S4" s="2" t="n">
-        <v>1354.375858</v>
+        <v>1337.197942</v>
       </c>
       <c r="T4" s="2" t="n">
         <f aca="false">Q4*S4</f>
-        <v>1354.375858</v>
+        <v>1337.197942</v>
       </c>
       <c r="U4" s="5" t="n">
         <f aca="false">AVERAGE(Q4, R4)</f>
-        <v>0.781</v>
+        <v>0.7545</v>
       </c>
       <c r="V4" s="3" t="n">
         <f aca="false">D4*E4*F4*G4*H4*I4*J4*K4*L4*M4*N4*O4*P4*1000</f>
         <v>1000</v>
       </c>
+      <c r="W4" s="2" t="n">
+        <v>704</v>
+      </c>
       <c r="X4" s="3" t="n">
         <f aca="false">V4*Q4*R4</f>
-        <v>562</v>
+        <v>509</v>
       </c>
       <c r="Y4" s="4" t="n">
         <f aca="false">R4/Q4</f>
-        <v>0.562</v>
+        <v>0.509</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A5" s="27" t="s">
+      <c r="A5" s="25" t="s">
         <v>29</v>
       </c>
-      <c r="B5" s="26" t="n">
+      <c r="B5" s="24" t="n">
         <v>1</v>
       </c>
       <c r="C5" s="1" t="n">
         <v>0</v>
       </c>
       <c r="D5" s="3" t="n">
-        <v>1</v>
+        <v>0.99</v>
       </c>
       <c r="E5" s="3" t="n">
         <v>1</v>
@@ -1391,47 +1493,50 @@
         <v>1</v>
       </c>
       <c r="Q5" s="4" t="n">
-        <v>1</v>
+        <v>0.999943478205053</v>
       </c>
       <c r="R5" s="4" t="n">
-        <v>0.509</v>
+        <v>0.563</v>
       </c>
       <c r="S5" s="2" t="n">
-        <v>1337.197942</v>
+        <v>1329.146493</v>
       </c>
       <c r="T5" s="2" t="n">
         <f aca="false">Q5*S5</f>
-        <v>1337.197942</v>
+        <v>1329.07136725447</v>
       </c>
       <c r="U5" s="5" t="n">
         <f aca="false">AVERAGE(Q5, R5)</f>
-        <v>0.7545</v>
+        <v>0.781471739102527</v>
       </c>
       <c r="V5" s="3" t="n">
         <f aca="false">D5*E5*F5*G5*H5*I5*J5*K5*L5*M5*N5*O5*P5*1000</f>
-        <v>1000</v>
+        <v>990</v>
+      </c>
+      <c r="W5" s="2" t="n">
+        <v>739</v>
       </c>
       <c r="X5" s="3" t="n">
         <f aca="false">V5*Q5*R5</f>
-        <v>509</v>
+        <v>557.33849644715</v>
       </c>
       <c r="Y5" s="4" t="n">
         <f aca="false">R5/Q5</f>
-        <v>0.509</v>
+        <v>0.56303182356928</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A6" s="25" t="s">
+      <c r="A6" s="20" t="s">
         <v>30</v>
       </c>
-      <c r="B6" s="26" t="n">
+      <c r="B6" s="24" t="n">
         <v>1</v>
       </c>
       <c r="C6" s="1" t="n">
         <v>0</v>
       </c>
       <c r="D6" s="3" t="n">
-        <v>0.99</v>
+        <v>1</v>
       </c>
       <c r="E6" s="3" t="n">
         <v>1</v>
@@ -1470,44 +1575,44 @@
         <v>1</v>
       </c>
       <c r="Q6" s="4" t="n">
-        <v>0.999943478205053</v>
+        <v>1</v>
       </c>
       <c r="R6" s="4" t="n">
-        <v>0.563</v>
+        <v>0.562</v>
       </c>
       <c r="S6" s="2" t="n">
-        <v>1329.146493</v>
+        <v>1354.375858</v>
       </c>
       <c r="T6" s="2" t="n">
         <f aca="false">Q6*S6</f>
-        <v>1329.07136725447</v>
+        <v>1354.375858</v>
       </c>
       <c r="U6" s="5" t="n">
         <f aca="false">AVERAGE(Q6, R6)</f>
-        <v>0.781471739102527</v>
+        <v>0.781</v>
       </c>
       <c r="V6" s="3" t="n">
         <f aca="false">D6*E6*F6*G6*H6*I6*J6*K6*L6*M6*N6*O6*P6*1000</f>
-        <v>990</v>
+        <v>1000</v>
       </c>
       <c r="W6" s="2" t="n">
-        <v>734</v>
+        <v>724</v>
       </c>
       <c r="X6" s="3" t="n">
         <f aca="false">V6*Q6*R6</f>
-        <v>557.33849644715</v>
+        <v>562</v>
       </c>
       <c r="Y6" s="4" t="n">
         <f aca="false">R6/Q6</f>
-        <v>0.56303182356928</v>
+        <v>0.562</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A7" s="27" t="s">
+      <c r="A7" s="25" t="s">
         <v>31</v>
       </c>
-      <c r="B7" s="26" t="n">
-        <v>2</v>
+      <c r="B7" s="24" t="n">
+        <v>1</v>
       </c>
       <c r="C7" s="1" t="n">
         <v>0</v>
@@ -1555,33 +1660,33 @@
         <v>1</v>
       </c>
       <c r="R7" s="4" t="n">
-        <v>0.496</v>
+        <v>0.524</v>
       </c>
       <c r="S7" s="2" t="n">
-        <v>1316.05153</v>
+        <v>1367.670305</v>
       </c>
       <c r="T7" s="2" t="n">
         <f aca="false">Q7*S7</f>
-        <v>1316.05153</v>
+        <v>1367.670305</v>
       </c>
       <c r="U7" s="5" t="n">
         <f aca="false">AVERAGE(Q7, R7)</f>
-        <v>0.748</v>
+        <v>0.762</v>
       </c>
       <c r="V7" s="3" t="n">
         <f aca="false">D7*E7*F7*G7*H7*I7*J7*K7*L7*M7*N7*O7*P7*1000</f>
         <v>1000</v>
       </c>
-      <c r="W7" s="2" t="n">
-        <v>743</v>
+      <c r="W7" s="1" t="n">
+        <v>718</v>
       </c>
       <c r="X7" s="3" t="n">
         <f aca="false">V7*Q7*R7</f>
-        <v>496</v>
+        <v>524</v>
       </c>
       <c r="Y7" s="4" t="n">
         <f aca="false">R7/Q7</f>
-        <v>0.496</v>
+        <v>0.524</v>
       </c>
     </row>
     <row r="1048576" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
@@ -1598,68 +1703,62 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E2:P1048576">
-    <cfRule type="cellIs" priority="4" operator="lessThan" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="13">
-      <formula>0.5</formula>
-    </cfRule>
-    <cfRule type="cellIs" priority="5" operator="greaterThan" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="14">
+    <cfRule type="cellIs" priority="4" operator="greaterThan" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="13">
       <formula>0.5</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="T8:T1048576 T2:T4">
-    <cfRule type="cellIs" priority="6" operator="greaterThan" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="15">
+    <cfRule type="cellIs" priority="5" operator="greaterThan" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="14">
       <formula>800</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="Q2:Q1048576">
-    <cfRule type="cellIs" priority="7" operator="greaterThan" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="15">
+    <cfRule type="cellIs" priority="6" operator="greaterThan" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="14">
       <formula>0.75</formula>
-    </cfRule>
-    <cfRule type="cellIs" priority="8" operator="lessThan" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="16">
-      <formula>0.6</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="W2:W1048576">
-    <cfRule type="cellIs" priority="9" operator="greaterThan" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="15">
+    <cfRule type="cellIs" priority="7" operator="greaterThan" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="14">
       <formula>600</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="U2:U1048576">
-    <cfRule type="cellIs" priority="10" operator="greaterThanOrEqual" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="15">
+    <cfRule type="cellIs" priority="8" operator="greaterThanOrEqual" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="14">
       <formula>0.55</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="V2:V1048576">
-    <cfRule type="cellIs" priority="11" operator="greaterThan" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="15">
+    <cfRule type="cellIs" priority="9" operator="greaterThan" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="14">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="X2:X1048576">
-    <cfRule type="cellIs" priority="12" operator="greaterThan" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="17">
+    <cfRule type="cellIs" priority="10" operator="greaterThan" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="15">
       <formula>100</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="Y2:Y1048576">
-    <cfRule type="cellIs" priority="13" operator="greaterThan" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="17">
+    <cfRule type="cellIs" priority="11" operator="greaterThan" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="15">
       <formula>0.5</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="T5:T7">
-    <cfRule type="cellIs" priority="14" operator="greaterThan" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="15">
+    <cfRule type="cellIs" priority="12" operator="greaterThan" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="14">
       <formula>800</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="R2:R1048576">
-    <cfRule type="cellIs" priority="15" operator="greaterThan" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="18">
+    <cfRule type="cellIs" priority="13" operator="greaterThan" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="16">
       <formula>0.45</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="S4">
-    <cfRule type="cellIs" priority="16" operator="greaterThan" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="12">
+    <cfRule type="cellIs" priority="14" operator="greaterThan" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="12">
       <formula>1100</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="Z2:Z1048576">
-    <cfRule type="cellIs" priority="17" operator="greaterThan" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="19">
+    <cfRule type="cellIs" priority="15" operator="greaterThan" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="17">
       <formula>800</formula>
     </cfRule>
   </conditionalFormatting>
@@ -1710,87 +1809,87 @@
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="13" t="s">
-        <v>1</v>
-      </c>
-      <c r="B1" s="14" t="s">
+      <c r="A1" s="11" t="s">
+        <v>1</v>
+      </c>
+      <c r="B1" s="12" t="s">
         <v>2</v>
       </c>
-      <c r="C1" s="14" t="s">
+      <c r="C1" s="12" t="s">
         <v>3</v>
       </c>
-      <c r="D1" s="16" t="s">
+      <c r="D1" s="14" t="s">
         <v>4</v>
       </c>
-      <c r="E1" s="15" t="s">
+      <c r="E1" s="13" t="s">
         <v>5</v>
       </c>
-      <c r="F1" s="15" t="s">
+      <c r="F1" s="13" t="s">
         <v>6</v>
       </c>
-      <c r="G1" s="15" t="s">
+      <c r="G1" s="13" t="s">
         <v>7</v>
       </c>
-      <c r="H1" s="15" t="s">
+      <c r="H1" s="13" t="s">
         <v>8</v>
       </c>
-      <c r="I1" s="15" t="s">
+      <c r="I1" s="13" t="s">
         <v>9</v>
       </c>
-      <c r="J1" s="15" t="s">
+      <c r="J1" s="13" t="s">
         <v>10</v>
       </c>
-      <c r="K1" s="15" t="s">
+      <c r="K1" s="13" t="s">
         <v>11</v>
       </c>
-      <c r="L1" s="15" t="s">
+      <c r="L1" s="13" t="s">
         <v>12</v>
       </c>
-      <c r="M1" s="15" t="s">
+      <c r="M1" s="13" t="s">
         <v>13</v>
       </c>
-      <c r="N1" s="15" t="s">
+      <c r="N1" s="13" t="s">
         <v>14</v>
       </c>
-      <c r="O1" s="15" t="s">
+      <c r="O1" s="13" t="s">
         <v>15</v>
       </c>
-      <c r="P1" s="15" t="s">
+      <c r="P1" s="13" t="s">
         <v>16</v>
       </c>
-      <c r="Q1" s="16" t="s">
+      <c r="Q1" s="14" t="s">
         <v>17</v>
       </c>
-      <c r="R1" s="17" t="s">
+      <c r="R1" s="15" t="s">
         <v>18</v>
       </c>
-      <c r="S1" s="18" t="s">
+      <c r="S1" s="16" t="s">
         <v>19</v>
       </c>
-      <c r="T1" s="18" t="s">
+      <c r="T1" s="16" t="s">
         <v>20</v>
       </c>
-      <c r="U1" s="19" t="s">
+      <c r="U1" s="17" t="s">
         <v>21</v>
       </c>
-      <c r="V1" s="20" t="s">
+      <c r="V1" s="18" t="s">
         <v>22</v>
       </c>
-      <c r="W1" s="21" t="s">
+      <c r="W1" s="19" t="s">
         <v>23</v>
       </c>
-      <c r="X1" s="22" t="s">
+      <c r="X1" s="20" t="s">
         <v>24</v>
       </c>
-      <c r="Y1" s="23" t="s">
+      <c r="Y1" s="21" t="s">
         <v>25</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A2" s="28" t="s">
+      <c r="A2" s="26" t="s">
         <v>32</v>
       </c>
-      <c r="B2" s="29" t="n">
+      <c r="B2" s="27" t="n">
         <v>99</v>
       </c>
       <c r="C2" s="1" t="n">
@@ -1866,10 +1965,10 @@
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A3" s="28" t="s">
+      <c r="A3" s="26" t="s">
         <v>33</v>
       </c>
-      <c r="B3" s="29" t="n">
+      <c r="B3" s="27" t="n">
         <v>99</v>
       </c>
       <c r="C3" s="1" t="n">
@@ -2024,10 +2123,10 @@
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A5" s="28" t="s">
+      <c r="A5" s="26" t="s">
         <v>35</v>
       </c>
-      <c r="B5" s="29" t="n">
+      <c r="B5" s="27" t="n">
         <v>99</v>
       </c>
       <c r="C5" s="1" t="n">
@@ -2196,53 +2295,53 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E1:P1048576">
-    <cfRule type="cellIs" priority="3" operator="lessThan" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="13">
+    <cfRule type="cellIs" priority="3" operator="lessThan" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="21">
       <formula>0.5</formula>
     </cfRule>
-    <cfRule type="cellIs" priority="4" operator="greaterThan" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="14">
+    <cfRule type="cellIs" priority="4" operator="greaterThan" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="13">
       <formula>0.5</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="T1:T1048576">
-    <cfRule type="cellIs" priority="5" operator="greaterThan" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="15">
+    <cfRule type="cellIs" priority="5" operator="greaterThan" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="14">
       <formula>800</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="Q1:Q1048576">
-    <cfRule type="cellIs" priority="6" operator="greaterThan" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="15">
+    <cfRule type="cellIs" priority="6" operator="greaterThan" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="14">
       <formula>0.75</formula>
     </cfRule>
-    <cfRule type="cellIs" priority="7" operator="lessThan" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="16">
+    <cfRule type="cellIs" priority="7" operator="lessThan" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="22">
       <formula>0.6</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="W1:W1048576">
-    <cfRule type="cellIs" priority="8" operator="greaterThan" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="15">
+    <cfRule type="cellIs" priority="8" operator="greaterThan" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="14">
       <formula>600</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="U1:U1048576">
-    <cfRule type="cellIs" priority="9" operator="greaterThan" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="15">
+    <cfRule type="cellIs" priority="9" operator="greaterThan" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="14">
       <formula>0.55</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="V1:V1048576">
-    <cfRule type="cellIs" priority="10" operator="greaterThan" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="15">
+    <cfRule type="cellIs" priority="10" operator="greaterThan" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="14">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="R1:R1048576">
-    <cfRule type="cellIs" priority="11" operator="greaterThan" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="17">
+    <cfRule type="cellIs" priority="11" operator="greaterThan" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="15">
       <formula>0.45</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="X1:X1048576">
-    <cfRule type="cellIs" priority="12" operator="greaterThan" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="17">
+    <cfRule type="cellIs" priority="12" operator="greaterThan" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="15">
       <formula>100</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="Y1:Y1048576">
-    <cfRule type="cellIs" priority="13" operator="greaterThan" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="17">
+    <cfRule type="cellIs" priority="13" operator="greaterThan" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="15">
       <formula>0.5</formula>
     </cfRule>
   </conditionalFormatting>
@@ -2265,91 +2364,96 @@
   <dimension ref="A1:W7"/>
   <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="13.8" customHeight="true" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="30" width="6.82"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="12" width="5.73"/>
-    <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="22" min="22" style="31" width="11.53"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="28" width="6.82"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="29" width="5.73"/>
+    <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="22" min="22" style="4" width="11.53"/>
+    <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="23" min="23" style="30" width="11.53"/>
   </cols>
   <sheetData>
-    <row r="1" s="12" customFormat="true" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="32"/>
-      <c r="B1" s="33"/>
-      <c r="C1" s="32"/>
-      <c r="D1" s="32" t="n">
+    <row r="1" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1" s="31"/>
+      <c r="B1" s="32"/>
+      <c r="C1" s="31"/>
+      <c r="D1" s="31" t="n">
         <f aca="false">MAX(D3:D40)</f>
         <v>1</v>
       </c>
-      <c r="E1" s="32" t="n">
+      <c r="E1" s="31" t="n">
         <f aca="false">MAX(E3:E40)</f>
         <v>1</v>
       </c>
-      <c r="F1" s="32" t="n">
+      <c r="F1" s="31" t="n">
         <f aca="false">MAX(F3:F40)</f>
         <v>1</v>
       </c>
-      <c r="G1" s="32" t="n">
+      <c r="G1" s="31" t="n">
         <f aca="false">MAX(G3:G40)</f>
         <v>1</v>
       </c>
-      <c r="H1" s="32" t="n">
+      <c r="H1" s="31" t="n">
         <f aca="false">MAX(H3:H40)</f>
         <v>1</v>
       </c>
-      <c r="I1" s="32" t="n">
+      <c r="I1" s="31" t="n">
         <f aca="false">MAX(I3:I40)</f>
         <v>1</v>
       </c>
-      <c r="J1" s="32" t="n">
+      <c r="J1" s="31" t="n">
         <f aca="false">MAX(J3:J40)</f>
         <v>1</v>
       </c>
-      <c r="K1" s="32" t="n">
+      <c r="K1" s="31" t="n">
         <f aca="false">MAX(K3:K40)</f>
         <v>1</v>
       </c>
-      <c r="L1" s="32" t="n">
+      <c r="L1" s="31" t="n">
         <f aca="false">MAX(L3:L40)</f>
         <v>1</v>
       </c>
-      <c r="M1" s="32" t="n">
+      <c r="M1" s="31" t="n">
         <f aca="false">MAX(M3:M40)</f>
         <v>1</v>
       </c>
-      <c r="N1" s="32" t="n">
+      <c r="N1" s="31" t="n">
         <f aca="false">MAX(N3:N40)</f>
         <v>1</v>
       </c>
-      <c r="O1" s="32" t="n">
+      <c r="O1" s="31" t="n">
         <f aca="false">MAX(O3:O40)</f>
         <v>1</v>
       </c>
-      <c r="P1" s="32" t="n">
+      <c r="P1" s="31" t="n">
         <f aca="false">MAX(P3:P40)</f>
         <v>1</v>
       </c>
-      <c r="Q1" s="32" t="n">
+      <c r="Q1" s="31" t="n">
         <f aca="false">MAX(Q3:Q40)</f>
         <v>1</v>
       </c>
-      <c r="R1" s="32" t="n">
+      <c r="R1" s="31" t="n">
         <f aca="false">MAX(R3:R40)</f>
         <v>0</v>
       </c>
-      <c r="S1" s="32" t="n">
+      <c r="S1" s="31" t="n">
         <f aca="false">MAX(S3:S40)</f>
         <v>1</v>
       </c>
-      <c r="T1" s="32" t="n">
+      <c r="T1" s="31" t="n">
         <f aca="false">MAX(T3:T40)</f>
         <v>0</v>
       </c>
-      <c r="U1" s="32" t="n">
+      <c r="U1" s="31" t="n">
         <f aca="false">MAX(U3:U40)</f>
         <v>0.5</v>
       </c>
-      <c r="V1" s="33" t="n">
+      <c r="V1" s="32" t="n">
         <f aca="false">MAX(V3:V40)</f>
         <v>0.54852335453657</v>
       </c>
+      <c r="W1" s="33" t="n">
+        <f aca="false">MAX(W3:W40)</f>
+        <v>739</v>
+      </c>
     </row>
     <row r="2" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="34" t="s">
@@ -2418,376 +2522,382 @@
       <c r="V2" s="38" t="s">
         <v>17</v>
       </c>
-      <c r="W2" s="21" t="s">
+      <c r="W2" s="39" t="s">
         <v>23</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="39" t="s">
-        <v>29</v>
-      </c>
-      <c r="B3" s="30" t="n">
+      <c r="A3" s="20" t="s">
+        <v>28</v>
+      </c>
+      <c r="B3" s="28" t="n">
         <v>0.132811</v>
       </c>
-      <c r="C3" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="D3" s="0" t="n">
-        <v>1</v>
-      </c>
-      <c r="E3" s="0" t="n">
-        <v>1</v>
-      </c>
-      <c r="F3" s="0" t="n">
-        <v>1</v>
-      </c>
-      <c r="G3" s="0" t="n">
-        <v>1</v>
-      </c>
-      <c r="H3" s="0" t="n">
-        <v>1</v>
-      </c>
-      <c r="I3" s="0" t="n">
-        <v>1</v>
-      </c>
-      <c r="J3" s="0" t="n">
-        <v>1</v>
-      </c>
-      <c r="K3" s="0" t="n">
-        <v>1</v>
-      </c>
-      <c r="L3" s="0" t="n">
-        <v>1</v>
-      </c>
-      <c r="M3" s="0" t="n">
-        <v>1</v>
-      </c>
-      <c r="N3" s="0" t="n">
-        <v>1</v>
-      </c>
-      <c r="O3" s="0" t="n">
-        <v>1</v>
-      </c>
-      <c r="P3" s="0" t="n">
-        <v>1</v>
-      </c>
-      <c r="Q3" s="0" t="n">
-        <v>1</v>
-      </c>
-      <c r="R3" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="S3" s="0" t="n">
-        <v>1</v>
-      </c>
-      <c r="T3" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="U3" s="0" t="n">
+      <c r="C3" s="29" t="n">
+        <v>0</v>
+      </c>
+      <c r="D3" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="E3" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="F3" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="G3" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="H3" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="I3" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="J3" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="K3" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="L3" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="M3" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="N3" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="O3" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="P3" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q3" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="R3" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="S3" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="T3" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="U3" s="1" t="n">
         <v>0.5</v>
       </c>
-      <c r="V3" s="31" t="n">
+      <c r="V3" s="4" t="n">
         <v>0.54852335453657</v>
       </c>
+      <c r="W3" s="30" t="n">
+        <f aca="false">Main!W5</f>
+        <v>739</v>
+      </c>
     </row>
     <row r="4" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="39" t="s">
+      <c r="A4" s="23" t="s">
+        <v>27</v>
+      </c>
+      <c r="B4" s="28" t="n">
+        <v>0.132316</v>
+      </c>
+      <c r="C4" s="29" t="n">
+        <v>0</v>
+      </c>
+      <c r="D4" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="E4" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="F4" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="G4" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="H4" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="I4" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="J4" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="K4" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="L4" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="M4" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="N4" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="O4" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="P4" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q4" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="R4" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="S4" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="T4" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="U4" s="1" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="V4" s="4" t="n">
+        <v>0.54852335453657</v>
+      </c>
+      <c r="W4" s="30" t="n">
+        <f aca="false">Main!W7</f>
+        <v>718</v>
+      </c>
+    </row>
+    <row r="5" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A5" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="B5" s="28" t="n">
+        <v>0.132271</v>
+      </c>
+      <c r="C5" s="29" t="n">
+        <v>0</v>
+      </c>
+      <c r="D5" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="E5" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="F5" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="G5" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="H5" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="I5" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="J5" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="K5" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="L5" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="M5" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="N5" s="1" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="O5" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="P5" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q5" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="R5" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="S5" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="T5" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="U5" s="1" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="V5" s="4" t="n">
+        <v>0.534958826011471</v>
+      </c>
+      <c r="W5" s="30" t="n">
+        <f aca="false">Main!W4</f>
+        <v>704</v>
+      </c>
+    </row>
+    <row r="6" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A6" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="B4" s="30" t="n">
-        <v>0.132316</v>
-      </c>
-      <c r="C4" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="D4" s="0" t="n">
-        <v>1</v>
-      </c>
-      <c r="E4" s="0" t="n">
-        <v>1</v>
-      </c>
-      <c r="F4" s="0" t="n">
-        <v>1</v>
-      </c>
-      <c r="G4" s="0" t="n">
-        <v>1</v>
-      </c>
-      <c r="H4" s="0" t="n">
-        <v>1</v>
-      </c>
-      <c r="I4" s="0" t="n">
-        <v>1</v>
-      </c>
-      <c r="J4" s="0" t="n">
-        <v>1</v>
-      </c>
-      <c r="K4" s="0" t="n">
-        <v>1</v>
-      </c>
-      <c r="L4" s="0" t="n">
-        <v>1</v>
-      </c>
-      <c r="M4" s="0" t="n">
-        <v>1</v>
-      </c>
-      <c r="N4" s="0" t="n">
-        <v>1</v>
-      </c>
-      <c r="O4" s="0" t="n">
-        <v>1</v>
-      </c>
-      <c r="P4" s="0" t="n">
-        <v>1</v>
-      </c>
-      <c r="Q4" s="0" t="n">
-        <v>1</v>
-      </c>
-      <c r="R4" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="S4" s="0" t="n">
-        <v>1</v>
-      </c>
-      <c r="T4" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="U4" s="0" t="n">
+      <c r="B6" s="28" t="n">
+        <v>0.133852</v>
+      </c>
+      <c r="C6" s="29" t="n">
+        <v>0</v>
+      </c>
+      <c r="D6" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="E6" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="F6" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="G6" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="H6" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="I6" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="J6" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="K6" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="L6" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="M6" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="N6" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="O6" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="P6" s="1" t="n">
         <v>0.5</v>
       </c>
-      <c r="V4" s="31" t="n">
-        <v>0.54852335453657</v>
-      </c>
-      <c r="W4" s="6" t="n">
-        <f aca="false">Main!W7</f>
-        <v>743</v>
-      </c>
-    </row>
-    <row r="5" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="0" t="s">
-        <v>28</v>
-      </c>
-      <c r="B5" s="30" t="n">
-        <v>0.132271</v>
-      </c>
-      <c r="C5" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="D5" s="0" t="n">
-        <v>1</v>
-      </c>
-      <c r="E5" s="0" t="n">
-        <v>1</v>
-      </c>
-      <c r="F5" s="0" t="n">
-        <v>1</v>
-      </c>
-      <c r="G5" s="0" t="n">
-        <v>1</v>
-      </c>
-      <c r="H5" s="0" t="n">
-        <v>1</v>
-      </c>
-      <c r="I5" s="0" t="n">
-        <v>1</v>
-      </c>
-      <c r="J5" s="0" t="n">
-        <v>1</v>
-      </c>
-      <c r="K5" s="0" t="n">
-        <v>1</v>
-      </c>
-      <c r="L5" s="0" t="n">
-        <v>1</v>
-      </c>
-      <c r="M5" s="0" t="n">
-        <v>1</v>
-      </c>
-      <c r="N5" s="0" t="n">
+      <c r="Q6" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="R6" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="S6" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="T6" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="U6" s="1" t="n">
         <v>0.5</v>
       </c>
-      <c r="O5" s="0" t="n">
-        <v>1</v>
-      </c>
-      <c r="P5" s="0" t="n">
-        <v>1</v>
-      </c>
-      <c r="Q5" s="0" t="n">
-        <v>1</v>
-      </c>
-      <c r="R5" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="S5" s="0" t="n">
-        <v>1</v>
-      </c>
-      <c r="T5" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="U5" s="0" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="V5" s="31" t="n">
-        <v>0.534958826011471</v>
-      </c>
-    </row>
-    <row r="6" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="0" t="s">
-        <v>27</v>
-      </c>
-      <c r="B6" s="30" t="n">
-        <v>0.133852</v>
-      </c>
-      <c r="C6" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="D6" s="0" t="n">
-        <v>1</v>
-      </c>
-      <c r="E6" s="0" t="n">
-        <v>1</v>
-      </c>
-      <c r="F6" s="0" t="n">
-        <v>1</v>
-      </c>
-      <c r="G6" s="0" t="n">
-        <v>1</v>
-      </c>
-      <c r="H6" s="0" t="n">
-        <v>1</v>
-      </c>
-      <c r="I6" s="0" t="n">
-        <v>1</v>
-      </c>
-      <c r="J6" s="0" t="n">
-        <v>1</v>
-      </c>
-      <c r="K6" s="0" t="n">
-        <v>1</v>
-      </c>
-      <c r="L6" s="0" t="n">
-        <v>1</v>
-      </c>
-      <c r="M6" s="0" t="n">
-        <v>1</v>
-      </c>
-      <c r="N6" s="0" t="n">
-        <v>1</v>
-      </c>
-      <c r="O6" s="0" t="n">
-        <v>1</v>
-      </c>
-      <c r="P6" s="0" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="Q6" s="0" t="n">
-        <v>1</v>
-      </c>
-      <c r="R6" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="S6" s="0" t="n">
-        <v>1</v>
-      </c>
-      <c r="T6" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="U6" s="0" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="V6" s="31" t="n">
+      <c r="V6" s="4" t="n">
         <v>0.521936878627375</v>
       </c>
-      <c r="W6" s="0" t="n">
+      <c r="W6" s="30" t="n">
         <f aca="false">Main!W3</f>
         <v>731</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="0" t="s">
-        <v>30</v>
-      </c>
-      <c r="B7" s="30" t="n">
+      <c r="A7" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="B7" s="28" t="n">
         <v>0.132477</v>
       </c>
-      <c r="C7" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="D7" s="0" t="n">
+      <c r="C7" s="29" t="n">
+        <v>0</v>
+      </c>
+      <c r="D7" s="1" t="n">
         <v>0.99</v>
       </c>
-      <c r="E7" s="0" t="n">
-        <v>1</v>
-      </c>
-      <c r="F7" s="0" t="n">
-        <v>1</v>
-      </c>
-      <c r="G7" s="0" t="n">
-        <v>1</v>
-      </c>
-      <c r="H7" s="0" t="n">
-        <v>1</v>
-      </c>
-      <c r="I7" s="0" t="n">
-        <v>1</v>
-      </c>
-      <c r="J7" s="0" t="n">
-        <v>1</v>
-      </c>
-      <c r="K7" s="0" t="n">
-        <v>1</v>
-      </c>
-      <c r="L7" s="0" t="n">
-        <v>1</v>
-      </c>
-      <c r="M7" s="0" t="n">
-        <v>1</v>
-      </c>
-      <c r="N7" s="0" t="n">
-        <v>1</v>
-      </c>
-      <c r="O7" s="0" t="n">
-        <v>1</v>
-      </c>
-      <c r="P7" s="0" t="n">
+      <c r="E7" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="F7" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="G7" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="H7" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="I7" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="J7" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="K7" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="L7" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="M7" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="N7" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="O7" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="P7" s="1" t="n">
         <v>0.5</v>
       </c>
-      <c r="Q7" s="0" t="n">
-        <v>1</v>
-      </c>
-      <c r="R7" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="S7" s="0" t="n">
-        <v>1</v>
-      </c>
-      <c r="T7" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="U7" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="V7" s="31" t="n">
+      <c r="Q7" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="R7" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="S7" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="T7" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="U7" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="V7" s="4" t="n">
         <v>0.378930047686369</v>
       </c>
-      <c r="W7" s="6" t="n">
+      <c r="W7" s="30" t="n">
         <f aca="false">Main!W6</f>
-        <v>734</v>
+        <v>724</v>
       </c>
     </row>
   </sheetData>
   <autoFilter ref="A2:W7"/>
   <conditionalFormatting sqref="D1:U1048576">
-    <cfRule type="cellIs" priority="2" operator="greaterThan" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="19">
+    <cfRule type="cellIs" priority="2" operator="greaterThan" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="17">
       <formula>0.5</formula>
     </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="D1:U1048576">
     <cfRule type="cellIs" priority="3" operator="lessThan" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="23">
       <formula>0.5</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="W2">
-    <cfRule type="cellIs" priority="4" operator="greaterThan" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="15">
+    <cfRule type="cellIs" priority="4" operator="greaterThan" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="14">
       <formula>600</formula>
     </cfRule>
   </conditionalFormatting>
@@ -2800,4 +2910,691 @@
   </headerFooter>
   <drawing r:id="rId1"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+  <sheetPr filterMode="false">
+    <pageSetUpPr fitToPage="false"/>
+  </sheetPr>
+  <dimension ref="A1:D31"/>
+  <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="12.8" customHeight="true" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetData>
+    <row r="1" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1" s="23" t="s">
+        <v>42</v>
+      </c>
+      <c r="B1" s="23" t="s">
+        <v>43</v>
+      </c>
+      <c r="C1" s="23" t="s">
+        <v>44</v>
+      </c>
+      <c r="D1" s="23" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="2" s="1" customFormat="true" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A2" s="40" t="s">
+        <v>45</v>
+      </c>
+      <c r="B2" s="40" t="n">
+        <v>7</v>
+      </c>
+      <c r="C2" s="40" t="n">
+        <v>1</v>
+      </c>
+      <c r="D2" s="40" t="n">
+        <v>682</v>
+      </c>
+    </row>
+    <row r="3" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A3" s="40" t="s">
+        <v>45</v>
+      </c>
+      <c r="B3" s="40" t="n">
+        <v>9</v>
+      </c>
+      <c r="C3" s="40" t="n">
+        <v>1</v>
+      </c>
+      <c r="D3" s="40" t="n">
+        <v>644</v>
+      </c>
+    </row>
+    <row r="4" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A4" s="40" t="n">
+        <v>2004</v>
+      </c>
+      <c r="B4" s="40" t="n">
+        <v>7</v>
+      </c>
+      <c r="C4" s="40" t="n">
+        <v>18</v>
+      </c>
+      <c r="D4" s="40" t="n">
+        <v>708</v>
+      </c>
+    </row>
+    <row r="5" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A5" s="1" t="n">
+        <v>2004</v>
+      </c>
+      <c r="B5" s="40" t="n">
+        <v>9</v>
+      </c>
+      <c r="C5" s="40" t="n">
+        <v>18</v>
+      </c>
+      <c r="D5" s="40" t="n">
+        <v>788</v>
+      </c>
+    </row>
+    <row r="6" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A6" s="1" t="n">
+        <v>2004</v>
+      </c>
+      <c r="B6" s="1" t="n">
+        <v>11</v>
+      </c>
+      <c r="C6" s="1" t="n">
+        <v>18</v>
+      </c>
+      <c r="D6" s="1" t="n">
+        <v>757</v>
+      </c>
+    </row>
+    <row r="7" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A7" s="1" t="n">
+        <v>2004</v>
+      </c>
+      <c r="B7" s="1" t="n">
+        <v>13</v>
+      </c>
+      <c r="C7" s="1" t="n">
+        <v>18</v>
+      </c>
+      <c r="D7" s="1" t="n">
+        <v>751</v>
+      </c>
+    </row>
+    <row r="8" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A8" s="1" t="n">
+        <v>2004</v>
+      </c>
+      <c r="B8" s="1" t="n">
+        <v>7</v>
+      </c>
+      <c r="C8" s="40" t="n">
+        <v>20</v>
+      </c>
+      <c r="D8" s="40" t="n">
+        <v>666</v>
+      </c>
+    </row>
+    <row r="9" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A9" s="1" t="n">
+        <v>2004</v>
+      </c>
+      <c r="B9" s="1" t="n">
+        <v>9</v>
+      </c>
+      <c r="C9" s="1" t="n">
+        <v>20</v>
+      </c>
+      <c r="D9" s="1" t="n">
+        <v>734</v>
+      </c>
+    </row>
+    <row r="10" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A10" s="1" t="n">
+        <v>2004</v>
+      </c>
+      <c r="B10" s="1" t="n">
+        <v>11</v>
+      </c>
+      <c r="C10" s="1" t="n">
+        <v>20</v>
+      </c>
+      <c r="D10" s="1" t="n">
+        <v>796</v>
+      </c>
+    </row>
+    <row r="11" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A11" s="1" t="n">
+        <v>2004</v>
+      </c>
+      <c r="B11" s="41" t="n">
+        <v>13</v>
+      </c>
+      <c r="C11" s="41" t="n">
+        <v>20</v>
+      </c>
+      <c r="D11" s="42" t="n">
+        <v>859</v>
+      </c>
+    </row>
+    <row r="12" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A12" s="1" t="n">
+        <v>2003</v>
+      </c>
+      <c r="B12" s="1" t="n">
+        <v>13</v>
+      </c>
+      <c r="C12" s="1" t="n">
+        <v>20</v>
+      </c>
+      <c r="D12" s="1" t="n">
+        <v>691</v>
+      </c>
+    </row>
+    <row r="13" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A13" s="1" t="n">
+        <v>2004</v>
+      </c>
+      <c r="B13" s="1" t="n">
+        <v>13</v>
+      </c>
+      <c r="C13" s="1" t="n">
+        <v>20</v>
+      </c>
+      <c r="D13" s="1" t="n">
+        <v>758</v>
+      </c>
+    </row>
+    <row r="14" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A14" s="40" t="n">
+        <v>2004</v>
+      </c>
+      <c r="B14" s="40" t="n">
+        <v>5</v>
+      </c>
+      <c r="C14" s="40" t="n">
+        <v>22</v>
+      </c>
+      <c r="D14" s="40" t="n">
+        <v>731</v>
+      </c>
+    </row>
+    <row r="15" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A15" s="1" t="n">
+        <v>2004</v>
+      </c>
+      <c r="B15" s="1" t="n">
+        <v>7</v>
+      </c>
+      <c r="C15" s="40" t="n">
+        <v>22</v>
+      </c>
+      <c r="D15" s="40" t="n">
+        <v>761</v>
+      </c>
+    </row>
+    <row r="16" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A16" s="1" t="n">
+        <v>2004</v>
+      </c>
+      <c r="B16" s="1" t="n">
+        <v>9</v>
+      </c>
+      <c r="C16" s="1" t="n">
+        <v>22</v>
+      </c>
+      <c r="D16" s="43" t="n">
+        <v>802</v>
+      </c>
+    </row>
+    <row r="17" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A17" s="1" t="n">
+        <v>2004</v>
+      </c>
+      <c r="B17" s="1" t="n">
+        <v>11</v>
+      </c>
+      <c r="C17" s="1" t="n">
+        <v>22</v>
+      </c>
+      <c r="D17" s="1" t="n">
+        <v>708</v>
+      </c>
+    </row>
+    <row r="18" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A18" s="1" t="n">
+        <v>2004</v>
+      </c>
+      <c r="B18" s="1" t="n">
+        <v>13</v>
+      </c>
+      <c r="C18" s="1" t="n">
+        <v>22</v>
+      </c>
+      <c r="D18" s="1" t="n">
+        <v>644</v>
+      </c>
+    </row>
+    <row r="19" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A19" s="1" t="n">
+        <v>2004</v>
+      </c>
+      <c r="B19" s="1" t="n">
+        <v>7</v>
+      </c>
+      <c r="C19" s="1" t="n">
+        <v>24</v>
+      </c>
+      <c r="D19" s="1" t="n">
+        <v>745</v>
+      </c>
+    </row>
+    <row r="20" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A20" s="1" t="n">
+        <v>2004</v>
+      </c>
+      <c r="B20" s="1" t="n">
+        <v>8</v>
+      </c>
+      <c r="C20" s="1" t="n">
+        <v>24</v>
+      </c>
+      <c r="D20" s="1" t="n">
+        <v>741</v>
+      </c>
+    </row>
+    <row r="21" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A21" s="1" t="n">
+        <v>2004</v>
+      </c>
+      <c r="B21" s="1" t="n">
+        <v>9</v>
+      </c>
+      <c r="C21" s="1" t="n">
+        <v>24</v>
+      </c>
+      <c r="D21" s="1" t="n">
+        <v>730</v>
+      </c>
+    </row>
+    <row r="22" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A22" s="1" t="n">
+        <v>2004</v>
+      </c>
+      <c r="B22" s="1" t="n">
+        <v>11</v>
+      </c>
+      <c r="C22" s="1" t="n">
+        <v>24</v>
+      </c>
+      <c r="D22" s="1" t="n">
+        <v>689</v>
+      </c>
+    </row>
+    <row r="23" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A23" s="1" t="n">
+        <v>2004</v>
+      </c>
+      <c r="B23" s="1" t="n">
+        <v>13</v>
+      </c>
+      <c r="C23" s="1" t="n">
+        <v>24</v>
+      </c>
+      <c r="D23" s="1" t="n">
+        <v>709</v>
+      </c>
+    </row>
+    <row r="24" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A24" s="1" t="n">
+        <v>2004</v>
+      </c>
+      <c r="B24" s="1" t="n">
+        <v>7</v>
+      </c>
+      <c r="C24" s="1" t="n">
+        <v>26</v>
+      </c>
+      <c r="D24" s="1" t="n">
+        <v>760</v>
+      </c>
+    </row>
+    <row r="25" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A25" s="1" t="n">
+        <v>2004</v>
+      </c>
+      <c r="B25" s="1" t="n">
+        <v>9</v>
+      </c>
+      <c r="C25" s="1" t="n">
+        <v>26</v>
+      </c>
+      <c r="D25" s="1" t="n">
+        <v>694</v>
+      </c>
+    </row>
+    <row r="26" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A26" s="1" t="n">
+        <v>2004</v>
+      </c>
+      <c r="B26" s="1" t="n">
+        <v>11</v>
+      </c>
+      <c r="C26" s="1" t="n">
+        <v>26</v>
+      </c>
+      <c r="D26" s="1" t="n">
+        <v>624</v>
+      </c>
+    </row>
+    <row r="27" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A27" s="1" t="n">
+        <v>2004</v>
+      </c>
+      <c r="B27" s="1" t="n">
+        <v>13</v>
+      </c>
+      <c r="C27" s="1" t="n">
+        <v>26</v>
+      </c>
+      <c r="D27" s="1" t="n">
+        <v>676</v>
+      </c>
+    </row>
+    <row r="28" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A28" s="1" t="n">
+        <v>2004</v>
+      </c>
+      <c r="B28" s="1" t="n">
+        <v>7</v>
+      </c>
+      <c r="C28" s="1" t="n">
+        <v>28</v>
+      </c>
+      <c r="D28" s="1" t="n">
+        <v>686</v>
+      </c>
+    </row>
+    <row r="29" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A29" s="1" t="n">
+        <v>2004</v>
+      </c>
+      <c r="B29" s="1" t="n">
+        <v>7</v>
+      </c>
+      <c r="C29" s="1" t="n">
+        <v>30</v>
+      </c>
+      <c r="D29" s="1" t="n">
+        <v>719</v>
+      </c>
+    </row>
+    <row r="30" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A30" s="1" t="n">
+        <v>2004</v>
+      </c>
+      <c r="B30" s="1" t="n">
+        <v>7</v>
+      </c>
+      <c r="C30" s="1" t="n">
+        <v>32</v>
+      </c>
+      <c r="D30" s="1" t="n">
+        <v>589</v>
+      </c>
+    </row>
+    <row r="31" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A31" s="1" t="n">
+        <v>2004</v>
+      </c>
+      <c r="B31" s="1" t="n">
+        <v>7</v>
+      </c>
+      <c r="C31" s="1" t="n">
+        <v>34</v>
+      </c>
+      <c r="D31" s="1" t="n">
+        <v>636</v>
+      </c>
+    </row>
+  </sheetData>
+  <autoFilter ref="A1:D31"/>
+  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
+  <pageMargins left="0.7875" right="0.7875" top="1.05277777777778" bottom="1.05277777777778" header="0.7875" footer="0.7875"/>
+  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <headerFooter differentFirst="false" differentOddEven="false">
+    <oddHeader>&amp;C&amp;"Times New Roman,Navadno"&amp;12&amp;Kffffff&amp;A</oddHeader>
+    <oddFooter>&amp;C&amp;"Times New Roman,Navadno"&amp;12&amp;KffffffPage &amp;P</oddFooter>
+  </headerFooter>
+  <drawing r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+  <sheetPr filterMode="false">
+    <pageSetUpPr fitToPage="false"/>
+  </sheetPr>
+  <dimension ref="A1:F6"/>
+  <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="12.8" customHeight="true" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetData>
+    <row r="1" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1" s="23" t="s">
+        <v>42</v>
+      </c>
+      <c r="B1" s="23" t="s">
+        <v>46</v>
+      </c>
+      <c r="C1" s="23" t="s">
+        <v>47</v>
+      </c>
+      <c r="D1" s="23" t="s">
+        <v>48</v>
+      </c>
+      <c r="E1" s="23" t="s">
+        <v>49</v>
+      </c>
+      <c r="F1" s="23" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="2" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A2" s="1" t="n">
+        <v>2004</v>
+      </c>
+      <c r="B2" s="41" t="n">
+        <v>13</v>
+      </c>
+      <c r="C2" s="41" t="n">
+        <v>20</v>
+      </c>
+      <c r="D2" s="41" t="n">
+        <v>13</v>
+      </c>
+      <c r="E2" s="41" t="n">
+        <v>20</v>
+      </c>
+      <c r="F2" s="42" t="n">
+        <v>859</v>
+      </c>
+    </row>
+    <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A3" s="1" t="n">
+        <v>2004</v>
+      </c>
+      <c r="B3" s="1" t="n">
+        <v>13</v>
+      </c>
+      <c r="C3" s="1" t="n">
+        <v>20</v>
+      </c>
+      <c r="D3" s="1" t="n">
+        <v>12</v>
+      </c>
+      <c r="E3" s="1" t="n">
+        <v>21</v>
+      </c>
+      <c r="F3" s="1" t="n">
+        <v>710</v>
+      </c>
+    </row>
+    <row r="4" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A4" s="1" t="n">
+        <v>2004</v>
+      </c>
+      <c r="B4" s="1" t="n">
+        <v>13</v>
+      </c>
+      <c r="C4" s="1" t="n">
+        <v>20</v>
+      </c>
+      <c r="D4" s="1" t="n">
+        <v>12</v>
+      </c>
+      <c r="E4" s="1" t="n">
+        <v>22</v>
+      </c>
+      <c r="F4" s="1" t="n">
+        <v>683</v>
+      </c>
+    </row>
+    <row r="5" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A5" s="1" t="n">
+        <v>2005</v>
+      </c>
+      <c r="B5" s="1" t="n">
+        <v>12</v>
+      </c>
+      <c r="C5" s="1" t="n">
+        <v>20</v>
+      </c>
+      <c r="D5" s="1" t="n">
+        <v>13</v>
+      </c>
+      <c r="E5" s="1" t="n">
+        <v>20</v>
+      </c>
+      <c r="F5" s="1" t="n">
+        <v>797</v>
+      </c>
+    </row>
+    <row r="6" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A6" s="1" t="n">
+        <v>2004</v>
+      </c>
+      <c r="B6" s="1" t="n">
+        <v>13</v>
+      </c>
+      <c r="C6" s="1" t="n">
+        <v>20</v>
+      </c>
+      <c r="D6" s="1" t="n">
+        <v>12</v>
+      </c>
+      <c r="E6" s="1" t="n">
+        <v>20</v>
+      </c>
+      <c r="F6" s="1" t="n">
+        <v>821</v>
+      </c>
+    </row>
+  </sheetData>
+  <autoFilter ref="A1:F2"/>
+  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
+  <pageMargins left="0.7875" right="0.7875" top="1.05277777777778" bottom="1.05277777777778" header="0.7875" footer="0.7875"/>
+  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <headerFooter differentFirst="false" differentOddEven="false">
+    <oddHeader>&amp;C&amp;"Times New Roman,Navadno"&amp;12&amp;Kffffff&amp;A</oddHeader>
+    <oddFooter>&amp;C&amp;"Times New Roman,Navadno"&amp;12&amp;KffffffPage &amp;P</oddFooter>
+  </headerFooter>
+  <drawing r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+  <sheetPr filterMode="false">
+    <pageSetUpPr fitToPage="false"/>
+  </sheetPr>
+  <dimension ref="A1:D5"/>
+  <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="12.8" customHeight="true" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetData>
+    <row r="1" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1" s="23" t="s">
+        <v>42</v>
+      </c>
+      <c r="B1" s="23" t="s">
+        <v>43</v>
+      </c>
+      <c r="C1" s="23" t="s">
+        <v>44</v>
+      </c>
+      <c r="D1" s="23" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="2" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A2" s="1" t="n">
+        <v>2004</v>
+      </c>
+      <c r="B2" s="41" t="n">
+        <v>13</v>
+      </c>
+      <c r="C2" s="41" t="n">
+        <v>20</v>
+      </c>
+      <c r="D2" s="42" t="n">
+        <v>859</v>
+      </c>
+    </row>
+    <row r="3" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A3" s="1" t="n">
+        <v>2004</v>
+      </c>
+      <c r="B3" s="1" t="n">
+        <v>13</v>
+      </c>
+      <c r="C3" s="1" t="n">
+        <v>20</v>
+      </c>
+      <c r="D3" s="1" t="n">
+        <v>758</v>
+      </c>
+    </row>
+    <row r="4" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A4" s="1" t="n">
+        <v>2004</v>
+      </c>
+      <c r="B4" s="1" t="n">
+        <v>13</v>
+      </c>
+      <c r="C4" s="1" t="n">
+        <v>20</v>
+      </c>
+      <c r="D4" s="0" t="n">
+        <v>762</v>
+      </c>
+    </row>
+    <row r="5" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A5" s="1" t="n">
+        <v>2004</v>
+      </c>
+      <c r="B5" s="1" t="n">
+        <v>13</v>
+      </c>
+      <c r="C5" s="1" t="n">
+        <v>20</v>
+      </c>
+      <c r="D5" s="0" t="n">
+        <v>761</v>
+      </c>
+    </row>
+  </sheetData>
+  <autoFilter ref="A1:D3"/>
+  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
+  <pageMargins left="0.7875" right="0.7875" top="1.05277777777778" bottom="1.05277777777778" header="0.7875" footer="0.7875"/>
+  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <headerFooter differentFirst="false" differentOddEven="false">
+    <oddHeader>&amp;C&amp;"Times New Roman,Navadno"&amp;12&amp;Kffffff&amp;A</oddHeader>
+    <oddFooter>&amp;C&amp;"Times New Roman,Navadno"&amp;12&amp;KffffffPage &amp;P</oddFooter>
+  </headerFooter>
+  <drawing r:id="rId1"/>
+</worksheet>
 </file>
--- a/Code/Jupiter/Connect4/Selected EVAL_PPO_results.xlsx
+++ b/Code/Jupiter/Connect4/Selected EVAL_PPO_results.xlsx
@@ -5,7 +5,7 @@
   <workbookPr backupFile="false" showObjects="all" date1904="false"/>
   <workbookProtection/>
   <bookViews>
-    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="5"/>
+    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="3"/>
   </bookViews>
   <sheets>
     <sheet name="Main" sheetId="1" state="visible" r:id="rId3"/>
@@ -2914,7 +2914,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-  <sheetPr filterMode="false">
+  <sheetPr filterMode="true">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:D31"/>
@@ -2934,7 +2934,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="2" s="1" customFormat="true" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="2" s="1" customFormat="true" ht="13.8" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="40" t="s">
         <v>45</v>
       </c>
@@ -2948,7 +2948,7 @@
         <v>682</v>
       </c>
     </row>
-    <row r="3" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="3" customFormat="false" ht="13.8" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="40" t="s">
         <v>45</v>
       </c>
@@ -2962,7 +2962,7 @@
         <v>644</v>
       </c>
     </row>
-    <row r="4" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="4" customFormat="false" ht="13.8" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="40" t="n">
         <v>2004</v>
       </c>
@@ -2976,7 +2976,7 @@
         <v>708</v>
       </c>
     </row>
-    <row r="5" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="5" customFormat="false" ht="13.8" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="1" t="n">
         <v>2004</v>
       </c>
@@ -2990,7 +2990,7 @@
         <v>788</v>
       </c>
     </row>
-    <row r="6" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="6" customFormat="false" ht="13.8" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="1" t="n">
         <v>2004</v>
       </c>
@@ -3018,7 +3018,7 @@
         <v>751</v>
       </c>
     </row>
-    <row r="8" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="8" customFormat="false" ht="13.8" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="1" t="n">
         <v>2004</v>
       </c>
@@ -3032,7 +3032,7 @@
         <v>666</v>
       </c>
     </row>
-    <row r="9" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="9" customFormat="false" ht="13.8" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="1" t="n">
         <v>2004</v>
       </c>
@@ -3046,7 +3046,7 @@
         <v>734</v>
       </c>
     </row>
-    <row r="10" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="10" customFormat="false" ht="13.8" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="1" t="n">
         <v>2004</v>
       </c>
@@ -3102,7 +3102,7 @@
         <v>758</v>
       </c>
     </row>
-    <row r="14" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="14" customFormat="false" ht="13.8" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="40" t="n">
         <v>2004</v>
       </c>
@@ -3116,7 +3116,7 @@
         <v>731</v>
       </c>
     </row>
-    <row r="15" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="15" customFormat="false" ht="13.8" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="1" t="n">
         <v>2004</v>
       </c>
@@ -3130,7 +3130,7 @@
         <v>761</v>
       </c>
     </row>
-    <row r="16" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="16" customFormat="false" ht="13.8" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="1" t="n">
         <v>2004</v>
       </c>
@@ -3144,7 +3144,7 @@
         <v>802</v>
       </c>
     </row>
-    <row r="17" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="17" customFormat="false" ht="13.8" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="1" t="n">
         <v>2004</v>
       </c>
@@ -3172,7 +3172,7 @@
         <v>644</v>
       </c>
     </row>
-    <row r="19" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="19" customFormat="false" ht="13.8" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="1" t="n">
         <v>2004</v>
       </c>
@@ -3186,7 +3186,7 @@
         <v>745</v>
       </c>
     </row>
-    <row r="20" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="20" customFormat="false" ht="13.8" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="1" t="n">
         <v>2004</v>
       </c>
@@ -3200,7 +3200,7 @@
         <v>741</v>
       </c>
     </row>
-    <row r="21" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="21" customFormat="false" ht="12.8" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A21" s="1" t="n">
         <v>2004</v>
       </c>
@@ -3214,7 +3214,7 @@
         <v>730</v>
       </c>
     </row>
-    <row r="22" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="22" customFormat="false" ht="12.8" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A22" s="1" t="n">
         <v>2004</v>
       </c>
@@ -3242,7 +3242,7 @@
         <v>709</v>
       </c>
     </row>
-    <row r="24" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="24" customFormat="false" ht="12.8" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A24" s="1" t="n">
         <v>2004</v>
       </c>
@@ -3256,7 +3256,7 @@
         <v>760</v>
       </c>
     </row>
-    <row r="25" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="25" customFormat="false" ht="12.8" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A25" s="1" t="n">
         <v>2004</v>
       </c>
@@ -3270,7 +3270,7 @@
         <v>694</v>
       </c>
     </row>
-    <row r="26" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="26" customFormat="false" ht="12.8" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A26" s="1" t="n">
         <v>2004</v>
       </c>
@@ -3298,7 +3298,7 @@
         <v>676</v>
       </c>
     </row>
-    <row r="28" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="28" customFormat="false" ht="12.8" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A28" s="1" t="n">
         <v>2004</v>
       </c>
@@ -3312,7 +3312,7 @@
         <v>686</v>
       </c>
     </row>
-    <row r="29" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="29" customFormat="false" ht="12.8" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A29" s="1" t="n">
         <v>2004</v>
       </c>
@@ -3326,7 +3326,7 @@
         <v>719</v>
       </c>
     </row>
-    <row r="30" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="30" customFormat="false" ht="12.8" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A30" s="1" t="n">
         <v>2004</v>
       </c>
@@ -3340,7 +3340,7 @@
         <v>589</v>
       </c>
     </row>
-    <row r="31" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="31" customFormat="false" ht="12.8" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A31" s="1" t="n">
         <v>2004</v>
       </c>
@@ -3355,7 +3355,13 @@
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:D31"/>
+  <autoFilter ref="A1:D31">
+    <filterColumn colId="1">
+      <filters>
+        <filter val="13"/>
+      </filters>
+    </filterColumn>
+  </autoFilter>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.7875" right="0.7875" top="1.05277777777778" bottom="1.05277777777778" header="0.7875" footer="0.7875"/>
   <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
@@ -3568,7 +3574,7 @@
       <c r="C4" s="1" t="n">
         <v>20</v>
       </c>
-      <c r="D4" s="0" t="n">
+      <c r="D4" s="1" t="n">
         <v>762</v>
       </c>
     </row>
@@ -3582,7 +3588,7 @@
       <c r="C5" s="1" t="n">
         <v>20</v>
       </c>
-      <c r="D5" s="0" t="n">
+      <c r="D5" s="1" t="n">
         <v>761</v>
       </c>
     </row>
